--- a/CW_Random_with_solution.xlsx
+++ b/CW_Random_with_solution.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,11 @@
           <t>Result</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ProblemID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,6 +455,9 @@
 </t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,6 +500,9 @@
 </t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>232</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,6 +551,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="5">
@@ -579,6 +593,9 @@
 </t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>234</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,6 +632,9 @@
 </t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,6 +666,9 @@
 </t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -682,6 +705,9 @@
 </t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,6 +732,9 @@
 </t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -747,6 +776,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -784,6 +816,9 @@
 </t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -816,6 +851,9 @@
 </t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -841,6 +879,9 @@
 </t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -873,6 +914,9 @@
 </t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -941,6 +985,9 @@
 </t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -969,6 +1016,9 @@
 </t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1001,6 +1051,9 @@
 </t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1029,6 +1082,9 @@
 </t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1049,6 +1105,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B19" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1078,6 +1137,9 @@
 </t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1101,6 +1163,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B21" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -1118,6 +1183,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B22" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -1148,6 +1216,9 @@
 </t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1182,6 +1253,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B24" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -1229,6 +1303,9 @@
 </t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1263,6 +1340,9 @@
 </t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1284,6 +1364,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B27" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -1330,6 +1413,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B28" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -1352,6 +1438,9 @@
 </t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1381,6 +1470,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B30" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -1422,6 +1514,9 @@
 </t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1434,6 +1529,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B32" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -1462,6 +1560,9 @@
 </t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1485,6 +1586,9 @@
 </t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1509,6 +1613,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B35" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="36">
@@ -1548,6 +1655,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B36" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -1584,6 +1694,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B37" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="38">
@@ -1612,6 +1725,9 @@
 </t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1698,6 +1814,9 @@
 </t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1730,6 +1849,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B40" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="41">
@@ -1753,6 +1875,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B41" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="42">
@@ -1801,6 +1926,9 @@
 </t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1823,6 +1951,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B43" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="44">
@@ -1845,6 +1976,9 @@
 </t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1873,6 +2007,9 @@
 </t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1891,6 +2028,9 @@
 </t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1923,6 +2063,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B47" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="48">
@@ -1991,6 +2134,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B48" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="49">
@@ -2017,6 +2163,9 @@
 </t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2070,6 +2219,9 @@
 </t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2101,6 +2253,9 @@
 }
 </t>
         </is>
+      </c>
+      <c r="B51" t="n">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/CW_Random_with_solution.xlsx
+++ b/CW_Random_with_solution.xlsx
@@ -432,23 +432,133 @@
       <c r="A2" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: You are driving a little too fast, and a police officer stops you. Write code to compute the result, encoded as an int value: 0=no ticket, 1=small ticket, or 2=big ticket. If speed is 60 or less, the result is 0. If speed is between 61 and 80 inclusive, the result is 1. If speed is 81 or more, the result is 2. Unless it is your birthday--on that day, your speed can be 5 higher in all cases.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int caughtSpeeding(int speed, boolean isBirthday)
 {
+ 	if(isBirthday == true)
+    {
+    	if(speed&lt;=65)
+        {
+        	return 0;
+        }
+        else if(speed&gt;= 66 &amp;&amp; speed&lt;=85)
+        {
+        	return 1;
+        }
+        else if(speed&gt;=86)
+        {
+        	return 2;
+        }
+    }
+    if(isBirthday == false)
+    {
+    	if(speed&lt;=60)
+        {
+        	return 0;
+        }
+        if(speed &gt;=61 &amp;&amp; speed&lt;=80)
+        {
+        	return 1;
+        }
+        if(speed&gt;=81)
+        {
+        	return 2;
+        }
+    }
+    return 1;
+}
+##Solution 2 is:
+public int caughtSpeeding(int speed, boolean isBirthday)
+{
+ if (isBirthday)
+     if (speed &lt;= 65)
+         return 0;
+    else if (speed &lt;= 85)
+        return 1;
+    else
+        return 2;
+ if (speed &lt;= 60)
+     return 0;
+    else if (speed &lt;= 80)
+        return 1;
+    else
+        return 2;
+}
+##Solution 3 is:
+public int caughtSpeeding(int speed, boolean isBirthday)
+{
+    int result;
+    if (isBirthday == true)
+    {
+        speed = speed - 5;
+    }
+    if (speed &lt;= 60)
+    {
+        return 0;
+    }
+    else if (speed &lt;= 80)
+    {
+        return 1;
+    }
+    else
+    {
+        return 2;
+    }
+}
+##Solution 4 is:
+public int caughtSpeeding(int speed, boolean isBirthday)
+{
+    int result = 0;
+    if (!isBirthday)
+    {
+      if (speed &lt;= 60)
+      {
+        result = 0;
+      }
+      else if (speed &gt;= 81)
+      {
+        result = 2;
+      }
+      else
+      {
+        result = 1;
+      }
+    }
     if (isBirthday)
     {
-        speed = speed - 5;
-    }
-    if (speed &lt;= 60)
-    {
+      if (speed &lt;= 65)
+      {
+        result = 0;
+      }
+      else if (speed &gt;= 86)
+      {
+        result = 2;
+      }
+      else
+      {
+          result = 1;
+      }
+    }
+ return result;  
+}
+##Solution 5 is:
+public int caughtSpeeding(int speed, boolean isBirthday)
+{
+    if(isBirthday) {
+        if(speed &lt;= 65) {
+            return 0;
+        } else if(66 &lt;= speed &amp;&amp; speed &lt;= 85) {
+            return 1;
+        } else if(86 &lt;=  speed) {
+            return 2;
+        }
+    }
+    if(speed &lt;= 60) {
         return 0;
-    }
-    else if (speed &lt;=80)
-    {
+    } else if(61 &lt;= speed &amp;&amp; speed &lt;= 80) {
         return 1;
-    }
-    else 
-    {
+    } else {
         return 2;
     }
 }
@@ -463,33 +573,91 @@
       <c r="A3" t="inlineStr">
         <is>
           <t xml:space="preserve">Given a day of the week encoded as 0 = Sun, 1 = Mon, 2 = Tue, ... 6 = Sat, and a boolean indicating if we are on vacation, return a string of the form "7:00" indicating when the alarm clock should ring. Weekdays, the alarm should be "7:00" and on the weekend it should be "10:00". Unless we are on vacation--then on weekdays it should be "10:00" and weekends it should be "off".
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String alarmClock(int day, boolean vacation)
 {
-    if (vacation == true)
-    {
-        if (day == 0)
-        {
-        	return "off";
-        }
-        else if (day == 6)
-        {
-        	return "off";
-        }
+    if(vacation)
+    {
+        if(day == 0 || day == 6)
+            return "off";
+        return "10:00";
+    }
+    else 
+    {
+        if(day == 0 || day == 6)
+            return "10:00";
+        return "7:00";
+    }
+}
+##Solution 2 is:
+public String alarmClock(int day, boolean vacation)
+{
+if(vacation) 
+{
+if(day == 0 || day == 6)
+return "off";
+else
+return "10:00";
+}
+if(day == 0 || day == 6)
+return "10:00";
+return "7:00";
+}
+##Solution 3 is:
+public String alarmClock(int day, boolean vacation)
+{
+    String time = "0:00";
+    if (day &gt; 0 &amp;&amp; day &lt; 6 &amp;&amp; !vacation) {
+        time = "7:00";
+    }
+    else if ((day == 0 || day == 6) &amp;&amp; !vacation) {
+     	time = "10:00";   
+    }
+    else if (day &gt; 0 &amp;&amp; day &lt; 6 &amp;&amp; vacation) {
+        time = "10:00";
+    }
+    else if ((day == 0 || day == 6) &amp;&amp; vacation) {
+     	time = "off";   
+    }
+    return time;
+}
+##Solution 4 is:
+public String alarmClock(int day, boolean vacation)
+{
+    if (vacation)
+    {
+        if (day == 0 || day == 6)
+            return "off";
         else
-        {
             return "10:00";
-        }
     }
     else
-    {
-    	if (day == 0)
-        {
-        	return "10:00";
-        }
-        else if (day == 6)
-        {
-        	return "10:00";
+        if (day == 0 || day == 6)
+            return "10:00";
+        else
+            return "7:00";
+}
+##Solution 5 is:
+public String alarmClock(int day, boolean vacation)
+{
+    boolean weekend = day == 6 || day ==0;
+    if(weekend)
+    {
+        if(vacation)
+        {
+            return "off";
+        }
+        else 
+        {
+            return "10:00";
+        }
+    }
+    else
+    {
+        if(vacation)
+        {
+            return "10:00";
         }
         else
         {
@@ -508,46 +676,79 @@
       <c r="A4" t="inlineStr">
         <is>
           <t xml:space="preserve">You and your date are trying to get a table at a restaurant. The parameter you is the stylishness of your clothes, in the range 0..10, and date is the stylishness of your date's clothes. Write a method that returns your chances of getting a table, encoded as an int value with 0 = no, 1 = maybe, 2 = yes. If either of you is very stylish, 8 or more, then the result is 2 (yes). With the exception that if either of you has style of 2 or less, then the result is 0 (no). Otherwise the result is 1 (maybe).
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int dateFashion(int you, int date)
 {
-    if (you &gt;= 8)
-    {
-        if (date &lt;= 2)
-        {
-            return 0;
-        }
-        else
-        {
-        	return 2;
-        }
-    }
-    else if (date &gt;= 8)
-    {
-        if (you &lt;= 2)
-        {
-            return 0;
-        }
-        else
-        {
-        	return 2;
-        }
-    }
-    else
-    {
-        if (you &lt;= 2)
-        {
-            return 0;
-        }
-        else if (date &lt;= 2)
-        {
-            return 0;
-        }
-        else
-        {
-        	return 1;
-        }
-    }
+   if (you &lt;= 2 || date &lt;= 2) return 0;
+    return (you &gt;= 8 &amp;&amp; date &gt;= 2 || date &gt;= 8 &amp;&amp; you &gt;= 2) ? 2 : 1;
+}
+##Solution 2 is:
+public int dateFashion(int you, int date)
+{
+   int table = 0;
+   if (you &lt;= 2 || date &lt;= 2)
+   {
+       table = 0;
+   }
+   else if (you &gt;= 8 || date &gt;= 8)
+   {
+       table = 2;
+   }
+   else
+   {
+       table = 1;
+   }
+    return table;
+}
+##Solution 3 is:
+public int dateFashion(int you, int date)
+{
+    if (you &lt;= 2 || date &lt;= 2)
+    {
+        return 0;
+    }
+    else if (you &gt;= 8 || date &gt;= 8)
+    {
+        return 2;
+    }
+    else 
+    {
+		return 1;
+    }
+}
+##Solution 4 is:
+public int dateFashion(int you, int date)
+{
+    int chance = 0;
+    if (you &lt;= 2 || date &lt;= 2){
+        chance = 0;
+    }
+    else if (you &gt;= 8 &amp;&amp; date &gt; 2){
+        chance = 2;
+    }
+    else if (you &gt; 2 &amp;&amp; date &gt;= 8){
+        chance = 2;
+    }
+    else if (you &lt; 8 &amp;&amp; you &gt; 2){
+         if (date &lt; 8 &amp;&amp; date &gt;2){
+              chance = 1;
+            }
+    }
+    return chance;
+}
+##Solution 5 is:
+public int dateFashion(int you, int date)
+{
+    if(you &lt;= 2 || date &lt;= 2)
+    {
+		return 0;
+    }
+	if(you &gt;= 8 || date &gt;= 8)
+    {
+		return 2;
+    }
+	return 1;
 }
 </t>
         </is>
@@ -560,35 +761,49 @@
       <c r="A5" t="inlineStr">
         <is>
           <t xml:space="preserve">When squirrels get together for a party, they like to have cigars. A squirrel party is successful when the number of cigars is between 40 and 60, inclusive. Unless it is the weekend, in which case there is no upper bound on the number of cigars. Return true if the party with the given values is successful, or false otherwise.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean cigarParty(int cigars, boolean isWeekend)
 {
     if (isWeekend)
-    {
-        if (cigars &gt;= 40)
-        {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
+        return (cigars &gt;= 40);
+    return (cigars &gt;= 40 &amp;&amp; cigars &lt;= 60);
+}
+##Solution 2 is:
+public boolean cigarParty(int cigars, boolean isWeekend)
+{
+    if (isWeekend == true &amp;&amp; cigars &gt;= 40)
+    {
+        return true;
+    }
+    if (!(isWeekend) &amp;&amp; cigars &gt;= 40 &amp;&amp; cigars &lt;=60)
+    {
+        return true;
     }
     else
     {
-        if (40 &lt;= cigars)
-        {
-            if (cigars &lt;= 60)
-            {
-                return true;
-            }
-            else
-        	{
-            	return false;
-        	}
-        }
         return false;
     }
+}
+##Solution 3 is:
+public boolean cigarParty(int cigars, boolean isWeekend)
+{
+	return cigars &gt;= 40 &amp;&amp; (cigars &lt;= 60 || isWeekend);
+}
+##Solution 4 is:
+public boolean cigarParty(int cigars, boolean isWeekend)
+{
+    if (isWeekend)
+    	return cigars &gt;= 40;
+    if (cigars &gt;= 40 &amp;&amp; cigars &lt;= 60)
+        return true;
+    else
+        return false;
+}
+##Solution 5 is:
+public boolean cigarParty(int cigars, boolean isWeekend)
+{
+    return ((cigars &gt;= 40 &amp;&amp; isWeekend) || (cigars &gt;= 40 &amp;&amp; cigars &lt;= 60));
 }
 </t>
         </is>
@@ -601,33 +816,88 @@
       <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">You have a green lottery ticket, with ints a, b, and c on it. If the numbers are all different from each other, the result is 0. If all of the numbers are the same, the result is 20. If two of the numbers are the same, the result is 10.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int greenTicket(int a, int b, int c)
 {
-    if (a != b)
-    {
-        if (a != c)
-        {
-            if (b != c)
-            {
-                return 0;
-            }
+    if(a == b)
+    {
+        if(b == c)
+            return 20;
+        return 10;
+    }
+    if(a == c || b == c)
+        return 10;
+    return 0;
+}
+##Solution 2 is:
+public int greenTicket(int a, int b, int c)
+{
+    if (a == b || b == c || a == c)
+    {
+        if (a == b &amp;&amp; b == c)
+        {
+            return 20;
+        }
+        else
+        {
             return 10;
         }
-        return 10;
     }
     else
     {
-        if (a == c)
-        {
-            if (b == c)
-            {
-                return 20;
-            }
-            return 10;
-        }
-        return 10;
-    }
+        return 0;
+    }
+}
+##Solution 3 is:
+public int greenTicket(int a, int b, int c)
+{
+    int result;
+    if ( a == b &amp;&amp; b == c)
+    {
+        result = 20;
+    }
+    else if (a == b || b == c || a == c)
+    {
+        result = 10;
+    }
+    else 
+    {
+        result = 0;
+    }
+    return result;
+}
+##Solution 4 is:
+public int greenTicket(int a, int b, int c)
+{
+    int lotteryWin = 0;
+    if ( a != b &amp;&amp; b!= c &amp;&amp; a!=c)
+    {
+    	return lotteryWin;
+    }
+    else if ( a == b &amp;&amp; b == c)
+    {
+    	lotteryWin = 20;
+        return lotteryWin;
+    }
+    else
+    {
+    	lotteryWin = 10;
+        return lotteryWin;
+    }
+}
+##Solution 5 is:
+public int greenTicket(int a, int b, int c)
+{
+    if(a == b)
+	{
+		if(b == c)
+			return 20;
+		return 10;
+	}
+	if(a == c || b == c)
+		return 10;
+	return 0;
 }
 </t>
         </is>
@@ -640,28 +910,73 @@
       <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Your cell phone rings. Return true if you should answer it. Normally you answer, except in the morning you only answer if it is your mom calling. In all cases, if you are asleep, you do not answer.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean answerCell(boolean isMorning, boolean isMom, boolean isAsleep)
 {
     if (isAsleep)
     {
         return false;
     }
-    if (isMorning)
-    {
-        if (isMom)
-        {
-        	return true;
-        }
-        else
-        {
-            return false;
-        }
+    else if (isMorning &amp;&amp; isMom)
+    {
+        return true;
+    }
+    else if (isMorning)
+    {
+        return false;
     }
     else
     {
         return true;
     }
+}
+##Solution 2 is:
+public boolean answerCell(boolean isMorning, boolean isMom, boolean isAsleep)
+{
+    if (isAsleep == true)
+    {
+        return false;
+    }
+    else if (isMorning == true &amp;&amp; isMom  == true)
+    {
+        return true;
+    }
+    else if (isMorning == true)
+    {
+        return false;
+    }
+    else
+    {
+        return true;
+    }
+}
+##Solution 3 is:
+public boolean answerCell(boolean isMorning, boolean isMom, boolean isAsleep)
+{
+    if(isAsleep)
+		return false;
+	if(isMom)
+		return true;
+	return (!isMorning);
+}
+##Solution 4 is:
+public boolean answerCell(boolean isMorning, boolean isMom, boolean isAsleep)
+{
+    if(isAsleep)
+		return false;
+	if(isMom)
+		return true;
+	return (!isMorning);
+}
+##Solution 5 is:
+public boolean answerCell(boolean isMorning, boolean isMom, boolean isAsleep)
+{
+	if(isAsleep)
+		return false;
+	if(isMom)
+		return true;
+	return (!isMorning);
 }
 </t>
         </is>
@@ -674,33 +989,98 @@
       <c r="A8" t="inlineStr">
         <is>
           <t xml:space="preserve">The number 6 is a truly great number. Given two int values, a and b, return true if either one is 6. Or if their sum or difference is 6. Note: the function Math.abs(num) computes the absolute value of a number.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean love6(int a, int b)
 {
-    if (a == 6)
-    {
+    if ( a == 6 || b == 6)
         return true;
-    }
-    else if (b == 6)
-    {
+    if (Math.abs(a - b) == 6 || a + b == 6)
         return true;
+    else
+            return false;
+}
+##Solution 2 is:
+public boolean love6(int a, int b)
+{
+   if (a == 6 || b == 6)
+   {
+       return true;
+   }
+   else if (a + b == 6)
+   {
+   		return true;   
+   }
+   else if (a - b == 6)
+   {
+		return true;
+   }
+   else if (b + a == 6)
+   {
+		return true;
+   }
+   else if (b - a == 6)
+   {
+       return true;
+   }
+   else
+   {
+    	return false;   
+   }
+}
+##Solution 3 is:
+public boolean love6(int a, int b)
+{
+    if (a == 6 || b == 6)
+    {
+        return true;
+    }
+    else if (Math.abs(a - b) == 6)
+    {
+        return true;
+    }
+    else if (Math.abs(b - a) == 6)
+    {
+        return true;
     }
     else if (a + b == 6)
     {
         return true;
     }
-    else if (a - b == 6)
-    {
+    else
+    {
+        return false;
+    }
+}
+##Solution 4 is:
+public boolean love6(int a, int b)
+{
+    if(a == 6 || b == 6)
         return true;
-    }
-    else if (b - a == 6)
-    {
+    else if(a+b == 6)
         return true;
+    else if(Math.abs(a-b) == 6)
+        return true;
+    else 
+        return false;
+}
+##Solution 5 is:
+private boolean is6;
+public boolean love6(int a, int b)
+{
+    if (a == 6 || b == 6)
+    {
+        is6 = true;
+    }
+    else if (a+b == 6 || a-b == 6 || b-a == 6)
+    {
+        is6 = true;
     }
     else
     {
-        return false;
-    }
+        is6 = false;
+    }
+    return is6;
 }
 </t>
         </is>
@@ -713,21 +1093,54 @@
       <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given 2 ints, a and b, return their sum. However, sums in the range 10..19 inclusive, are forbidden, so in that case just return 20.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int sortaSum(int a, int b)
 {
-    if (a + b &gt;= 10)
-    {
-        if (a + b &lt;= 19)
-        {
-            return 20;
-        }
-        return a + b;
-    }
-    else
-    {
-        return a + b;
-    }
+    if ((a + b) &gt;= 10 &amp;&amp; (a + b) &lt;= 19) 
+    {
+        return 20;
+    }
+	else
+    {
+    	return (a + b); 
+        // true if a+b is not between 10 and 19
+    }
+}
+##Solution 2 is:
+public int sortaSum(int a, int b)
+{
+    if((a+b)&gt;=10&amp;&amp;(a+b)&lt;=19)return 20;
+    return(a+b);
+}
+##Solution 3 is:
+public int sortaSum(int a, int b)
+{
+    if ((a + b &gt;= 10) &amp;&amp; (a + b &lt;= 19))
+        return 20;
+    else 
+        return a + b; 
+}
+##Solution 4 is:
+public int sortaSum(int a, int b)
+{
+    if (((a + b) &gt;= 10) &amp;&amp; ((a + b) &lt;= 19))
+    {
+        return 20;
+    }
+    else 
+        return (a + b);
+}
+##Solution 5 is:
+private int sum; 
+public int sortaSum(int a, int b)
+{
+    sum = a + b; 
+    if ((a + b) &lt;= 19 &amp;&amp; (a + b) &gt;= 10)
+    {
+        sum = 20; 
+    }
+    return sum; 
 }
 </t>
         </is>
@@ -740,39 +1153,103 @@
       <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given a number n, return true if n is in the range 1..10, inclusive. Unless "outsideMode" is true, in which case return true if the number is less or equal to 1, or greater or equal to 10.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean in1To10(int n, boolean outsideMode)
 {
-    if (outsideMode)
+    boolean in1to10;
+    if ((outsideMode == false) &amp;&amp; ((n &gt;= 1) &amp;&amp; (n &lt;= 10)))
+    {
+        in1to10 = true;
+    }
+    else if ((outsideMode) &amp;&amp; ((n &lt;= 1) || (n &gt;= 10)))
+    {
+        in1to10 = true;
+    }
+    else
+    {
+        in1to10 = false;
+    }
+    return in1to10;     
+}
+##Solution 2 is:
+public boolean in1To10(int n, boolean outsideMode)
+{
+    if (!outsideMode)
+    {
+        if (n &gt;= 1 &amp;&amp; n &lt;= 10)
+        {
+            return true;
+        }
+        else
+            return false;
+    }
+    else
+        if (n &lt;= 1 || n &gt;= 10)
+        {
+            return true;
+        }
+    	else
+        	return false;
+}
+##Solution 3 is:
+public boolean in1To10(int n, boolean outsideMode)
+{
+    if(outsideMode)
+        return(n &lt;= 1 || n &gt;= 10);
+    return(n &gt;= 1 &amp;&amp; n &lt;= 10);
+}
+##Solution 4 is:
+public boolean in1To10(int n, boolean outsideMode)
+{
+	if(outsideMode == false)
+    {
+        if(n&gt;=1 &amp;&amp; n&lt;=10)
+        {
+            return true;
+        }
+        else
+        {
+            return false;
+        }
+    }        
+    if(outsideMode == true)
+    {
+    	if(n&lt;= 1 || n&gt;=10)
+        {
+        	return true;
+        }
+        else
+        {
+        	return false;
+        }
+    }
+    return true;
+}
+##Solution 5 is:
+public boolean in1To10(int n, boolean outsideMode)
+{
+    boolean range = false;
+    if (n &gt;= 1 &amp;&amp; n &lt;= 10)
+    {
+        range = true;
+    }
+    if (outsideMode == true)
     {
         if (n &lt;= 1)
-        {
-            return true;
+        { 
+            range = true;
         }
         else if (n &gt;= 10)
         {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
-    }
-    else 
-    {
-        if (n &lt; 1)
-        {
-            return false;
-        }
-        else if (n &gt; 10)
-        {
-            return false;
-        }
-        else
-        {
-            return true;
-        }
-    }
+            range = true;
+        }
+        else 
+        {
+            range = false;
+        }
+    }
+    return range;
 }
 </t>
         </is>
@@ -785,33 +1262,72 @@
       <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: The squirrels in Palo Alto spend most of the day playing. In particular, they play if the temperature is between 60 and 90 (inclusive). Unless it is summer, then the upper limit is 100 instead of 90. Given an int temperature and a boolean isSummer, return true if the squirrels play and false otherwise.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean squirrelPlay(int temp, boolean isSummer)
 {
-    if (isSummer)
-    {
-        if (temp &gt;= 60)
-        {
-            if (temp &lt;= 100)
+    if(isSummer)
+    {
+		if (temp &gt;= 60 &amp;&amp; temp &lt;= 100)
+            return true;
+    }
+   if(!isSummer &amp;&amp; 60 &lt;= temp &amp;&amp; temp &lt;= 90)
+   {
+        return true;
+   }
+    else
+        return false;
+}
+##Solution 2 is:
+public boolean squirrelPlay(int temp, boolean isSummer)
+{
+    if (temp &gt;= 60 &amp;&amp; temp &lt;= 90)
+        return true;
+    else if ((temp &gt;= 60 &amp;&amp; temp &lt;= 100) &amp;&amp; isSummer == true)
+        return true;
+    else
+        return false;
+}
+##Solution 3 is:
+public boolean squirrelPlay(int temp, boolean isSummer)
+{
+    if (temp &lt; 60)
+        return false;
+    else if (temp &lt;= 90)
+        return true;
+    else if (temp &lt;= 100 &amp;&amp; isSummer)
+        return true;
+    else 
+        return false;
+}
+##Solution 4 is:
+public boolean squirrelPlay(int temp, boolean isSummer)
+{
+    if(isSummer &amp;&amp; 60 &lt;= temp &amp;&amp; temp &lt;= 100)
+        return true;
+    if(!isSummer &amp;&amp; 60 &lt;= temp &amp;&amp; temp &lt;= 90)
+        return true;
+    return false;
+}
+##Solution 5 is:
+public boolean squirrelPlay(int temp, boolean isSummer)
+{
+    boolean play = false;
+    if (isSummer == true)
+    {
+     if (temp &gt;59 &amp;&amp; temp&lt;101)
+     {
+         play = true;
+     }
+    }
+        else
+        {
+            if (temp&gt; 59 &amp;&amp; temp&lt;91)
             {
-                return true;
+                play = true;
             }
-            return false;
-        }
-        return false;
-    }
-    else
-    {
-        if (temp &gt;= 60)
-        {
-            if (temp &lt;= 90)
-            {
-                return true;
-            }
-            return false;
-        }
-        return false;
-    }
+    }
+    return play;
 }
 </t>
         </is>
@@ -824,22 +1340,111 @@
       <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given 2 int values greater than 0, return whichever value is nearest to 21 without going over. Return 0 if they both go over.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int blackjack(int a, int b)
 {
+    if(a &gt; 21 &amp;&amp; b &gt; 21)
+        return 0;
+    if(a &gt; 21)
+        return b;
+    if(b &gt; 21)
+        return a;
+    return a &gt; b ? a : b;
+}
+##Solution 2 is:
+public int blackjack(int a, int b)
+{
+    if ( a &gt; 21 &amp;&amp; b &gt; 21){
+        return 0;
+    }
+    else if ( b &gt; 21){
+        return a;
+    }
+    else if ( a &gt; 21){
+        return b;
+    }
+    if ((21 - a) &gt; (21 - b)){
+        return b;
+    }
+    else 
+    {
+        return a;}
+}
+##Solution 3 is:
+public int blackjack(int a, int b)
+{
+    if (a &gt; 21)
+    {
+        if (b &gt; 21)
+        {
+            return 0;
+        }
+        else
+        {
+            return b;
+        }
+    }
+    else if (a &lt; b &amp;&amp; b &lt;= 21)
+    {
+    	return b;
+    }
+    else
+    {
+        return a;
+    }     
+}
+##Solution 4 is:
+public int blackjack(int a, int b)
+{
+    if(a &gt; 21 &amp;&amp; b &gt; 21)
+    {
+        return 0;
+    }
+    else
+    {
+        int distA = a - 21;
+        int distB = b - 21;
+        if (distA &gt; distB)
+        {
+            if(a &lt;= 21)
+            {
+                return a;
+            }
+            else
+            {
+                return b;
+            }
+        }
+        else
+        {
+            if(b &lt;= 21)
+            {
+                return b;
+            }
+            else
+            {
+                return a;
+            }
+        }
+    }
+}
+##Solution 5 is:
+public int blackjack(int a, int b)
+{
     if (a &gt; 21 &amp;&amp; b &gt; 21)
     {
         return 0;
     }
-    else if (a &gt; 21)
-    {
-        return b;
-    }
-    else if (b &gt; 21)
-    {
-        return a;
-    }
-    else if (a &gt; b)
+    else if (a &lt; 21 &amp;&amp; b &gt; 21)
+    {
+     	return a;   
+    }
+    else if (b &lt; 21 &amp;&amp; a &gt; 21)
+    {
+     	return b;   
+    }
+    else if (a &gt;  b)
     {
         return a;
     }
@@ -859,21 +1464,90 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">For this problem, we'll round an int value up to the next multiple of 10 if its rightmost digit is 5 or more, so 15 rounds up to 20. Alternately, round down to the previous multiple of 10 if its rightmost digit is less than 5, so 12 rounds down to 10. Given 3 ints, a, b, and c, return the sum of their rounded values. To avoid code repetition, write a separate helper public int round10(int num) and call it 3 times. Write the helper entirely below and at the same indent level as roundSum().
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int roundSum(int a, int b, int c)
 {
     return round10(a) + round10(b) + round10(c);
 }
 public int round10(int num)
 {
-    int x = num % 10;
-    if (x &gt;= 5)
-    {
-        return num + (10 - x);
+    int nm = num % 10;
+    if (nm &gt;= 5)
+    {
+        return num + 10 - nm;
     }
     else
     {
-        return num - x;
+        return num - nm;
+    }
+}
+##Solution 2 is:
+public int roundSum(int a, int b, int c)
+{
+    int sunm = 0;
+    sunm = round10(a) + sunm;
+    sunm = round10(b) + sunm;
+    sunm = round10(c) + sunm;
+    return sunm;
+}
+public int round10(int num)
+{
+    int o = num;
+    while (num &gt; 10)
+    {
+        num = num - 10;
+    }
+    if (num &gt;= 5)
+    {
+        o = o - num + 10;
+        return o;
+    }
+    else
+    {
+        o = o - num;
+        return o;
+    }
+}
+##Solution 3 is:
+public int roundSum(int a, int b, int c)
+{
+    return round10(a) + round10(b) + round10(c);
+}
+public int round10(int num)
+{
+    int rd = num % 10;
+    if(rd &gt;= 5)
+        return num + 10 - rd;
+    return num - rd;
+}
+##Solution 4 is:
+public int roundSum(int a, int b, int c)
+{
+   return (round10(a) + round10(b) + round10(c));
+}
+public int round10(int num)
+{
+    return ((num + 5) - (num+5)%10);
+}
+##Solution 5 is:
+int sumNums;
+int modNum;
+public int roundSum(int a, int b, int c)
+{
+    sumNums = round10(a) + round10(b) + round10(c);
+    return sumNums;
+}
+public int round10(int num)
+{
+    modNum = num % 10;
+    if (modNum &gt;= 5)
+    {
+     	return num - modNum + 10;   
+    }
+    else
+    {
+       return num - modNum; 
     }
 }
 </t>
@@ -887,29 +1561,82 @@
       <c r="A14" t="inlineStr">
         <is>
           <t xml:space="preserve">We want make a package of goal kilos of chocolate. We have small bars (1 kilo each) and big bars (5 kilos each). Return the number of small bars to use, assuming we always use big bars before small bars. Return -1 if it can't be done.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int makeChocolate(int small, int big, int goal)
 {
-    if (goal &lt; 5)
-    {
-        return small;
-    }
-    else if (goal == big*5)
-    {
-        return 0;
-    }
-    else if (5*big &lt; goal &amp;&amp; (5*big + small) &gt;= goal)
-    {
-    	return goal - 5*big;
-    }
-    else if (5*big &gt; goal &amp;&amp; small + (big - 1)*5 &gt;= goal)
-    {
-        return goal - 5;
-    }
+    if(goal &gt;= 5)
+            if (goal/5 &gt;= big)
+                goal-= big * 5;
+        else
+                goal = goal % 5;
+        if(goal &lt;= small) 
+            return goal;
+        return -1;
+}
+##Solution 2 is:
+public int makeChocolate(int small, int big, int goal)
+{
+    int biggestGoal = goal / 5;
+    if (biggestGoal &lt;= big)
+        goal -= biggestGoal * 5;
     else
-    {
+        goal -= big * 5;
+    if (goal &lt;= small)
+        return goal;
+    return -1;
+}
+##Solution 3 is:
+int barsLeft;
+public int makeChocolate(int small, int big, int goal)
+{
+    barsLeft = goal % 5;
+    if ((big * 5) + small &lt; goal || small &lt; barsLeft)
+    {
+     	return -1;   
+    }
+    else if ((big * 5) &gt; goal)
+    {
+     	return barsLeft;   
+    }
+    else
+    {
+     	return goal - (big * 5);   
+    }
+}
+##Solution 4 is:
+public int makeChocolate(int small, int big, int goal)
+{
+    int required = goal - big*5;
+    if (big &lt;= goal/5 &amp;&amp; small &gt;= required)
+    {
+        return required;
+    }
+    else if (big &gt;= goal/5 &amp;&amp; small &gt;= goal % 5)
+    {
+        return goal % 5;
+    }
+    else 
+    {
+    	return -1;
+    }
+}
+##Solution 5 is:
+public int makeChocolate(int small, int big, int goal)
+{    
+    if(goal &gt;= 5)
+    {
+        if(goal/5 &gt;= big)
+        {
+            goal-= big * 5;
+        }
+        else
+        {
+            goal = goal % 5;
+        }
+    }
+        if(goal &lt;= small) return goal;
         return -1;
-    }
 }
 </t>
         </is>
@@ -922,9 +1649,31 @@
       <c r="A15" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given three ints, a, b, and c, one of them is small, one is medium and one is large. Return true if the three values are evenly spaced, so the difference between small and medium is the same as the difference between medium and large.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean evenlySpaced(int a, int b, int c)
 {
+    int temp;
+    if (a &gt;b ) {
+        temp =a;
+        a = b;
+        b = temp;
+    }
+    if (b &gt; c) {
+        temp = b;
+        b = c;
+        c = temp;
+    }
+    if (a &gt; b) {
+        temp =a;
+        a = b;
+        b = temp;
+    }
+    return b - a == c - b;
+}
+##Solution 2 is:
+public boolean evenlySpaced(int a, int b, int c)
+{
     if (a == b &amp;&amp; b == c)
     {
         return true;
@@ -981,6 +1730,83 @@
     {
         return false;
     }
+}
+##Solution 3 is:
+public boolean evenlySpaced(int a, int b, int c)
+{
+    if (b - a == c - b)
+    {
+        return true;
+    }
+     if (a - b == c - a)
+    {
+        return true;
+    }
+     if (a - c == c - b)
+    {
+        return true;
+    }
+     if (b - c == c - a)
+    {
+        return true;
+    } 
+    if (b - a == a - c)
+    {
+        return true;
+    }
+    if (a - b == b - c)
+    {
+        return true;
+    }
+    return false;
+}
+##Solution 4 is:
+public boolean evenlySpaced(int a, int b, int c)
+{
+    int placeHolder = 0;
+    if (a &gt; b)
+    {
+        placeHolder = a;
+        a = b;
+        b = placeHolder;
+    }
+    if (b &gt; c)
+    {
+        placeHolder = b;
+        b = c;
+        c = placeHolder;
+    }
+    if (a &gt; b)
+    {
+        placeHolder = a;
+        a = b;
+        b = placeHolder;
+    }
+    return b - a == c - b;
+}
+##Solution 5 is:
+public boolean evenlySpaced(int a, int b, int c)
+{
+    int temp;
+    if (b &lt; a) //when b lss than a
+    {
+        temp = b;
+        b = a;
+        a = temp;
+    }
+    if (c &lt; b) //when c less than b
+    {
+        temp = c;
+        c = b;
+        b = temp;
+    } 
+    if (b &lt; a) //when b less than a
+    {
+        temp = b;
+        b = a;
+        a = temp;
+    }
+    return a - b == b - c; //difference between a and b is equal to the difference b and c
 }
 </t>
         </is>
@@ -993,25 +1819,92 @@
       <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given 3 int values, a, b, and c, return their sum. However, if one of the values is 13 then it does not count towards the sum and values to its right do not count. So for example, if b is 13, then both b and c do not count.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int luckySum(int a, int b, int c)
 {
-    if (a != 13 &amp;&amp; b != 13 &amp;&amp; c != 13)
+    if (a==13)
+    {
+        return 0;
+    }
+    else if (b==13)
+    {
+        return a;
+    }
+    else if (c==13)
+    {
+        return a+b;
+    }
+    else
+        return a+b+c;
+}
+##Solution 2 is:
+public int luckySum(int a, int b, int c)
+{
+    if (a == 13){
+    	return(0);
+    }else{
+    	if(b == 13){
+        	return(a);
+        }else{
+        	if (c == 13){
+            	return(a + b);
+            }else{
+            	return(a + b + c);
+            }
+        }
+    }
+}
+##Solution 3 is:
+public int luckySum(int a, int b, int c)
+{
+    if (a==13)
+    {
+        return 0;
+    }
+    else if (b==13)
+    {
+        return a;
+    }
+    else if (c==13)
+    {
+        return a+b;
+    }
+    else
     {
         return a + b + c;
     }
-    else if (a == 13)
+}
+##Solution 4 is:
+public int luckySum(int a, int b, int c)
+{
+    if(a == 13)
     {
         return 0;
     }
-    else if (b == 13)
+    if(b == 13)
     {
         return a;
     }
-    else
-    {
-        return a + b;
-    }
+    if(c == 13)
+    {
+        return (a + b);
+    }
+    else 
+    {
+        return (a + b + c);
+    }
+}
+##Solution 5 is:
+public int luckySum(int a, int b, int c)
+{
+    if(a == 13)
+		return 0;
+	if(b == 13)
+		return a;
+	if(c == 13)
+		return (a + b);
+	return (a + b + c);
 }
 </t>
         </is>
@@ -1024,29 +1917,85 @@
       <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given 3 int values, a, b, and c, return their sum. However, if one of the values is the same as another of the values, it does not count towards the sum.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int loneSum(int a, int b, int c)
 {
-    if (a != b &amp;&amp; b != c &amp;&amp; a != c)
-    {
+    if(a == b)
+	{
+    	if(a == c)
+    	  return 0;
+    	return c;
+  	}
+  	if(a == c)
+    	return b; 
+  	if(b == c)
+    	return a;
+  return (a + b + c);
+}
+##Solution 2 is:
+public int loneSum(int a, int b, int c)
+{
+    if (a != b &amp;&amp; b != c &amp;&amp; a != c) {
         return a + b + c;
     }
-    else if (a == b &amp;&amp; b == c)
-    {
+    else if (a == b &amp;&amp; a != c) {
+        return c;
+    }
+    else if (a == c &amp;&amp; b != c) {
+        return b;
+    }
+    else if (b == c &amp;&amp; b != c) {
+        return a;
+    }
+    else if (a == b &amp;&amp; b == c &amp;&amp; a == c) {
         return 0;
     }
-    else if (a == b)
-    {
-        return c;
-    }
-    else if (a == c)
-    {
-        return b;
-    }
-    else
-    {
-        return a;
-    }
+return a;}
+##Solution 3 is:
+public int loneSum(int a, int b, int c)
+{
+  if(a == b)
+	{
+    	if(a == c)
+    	  return 0;
+    	return c;
+  	}
+  	if(a == c)
+    	return b; 
+  	if(b == c)
+    	return a;
+  return (a + b + c);
+}
+##Solution 4 is:
+public int loneSum(int a, int b, int c)
+{
+    if(a == b)
+	{
+    	if(a == c)
+    	  return 0;
+    	return c;
+  	}
+  	if(a == c)
+    	return b; 
+  	if(b == c)
+    	return a;
+  return (a + b + c);
+}
+##Solution 5 is:
+public int loneSum(int a, int b, int c)
+{
+    if(a == b)
+	{
+    	if(a == c)
+    	  return 0;
+    	return c;
+  	}
+  	if(a == c)
+    	return b; 
+  	if(b == c)
+    	return a;
+	return (a + b + c);
 }
 </t>
         </is>
@@ -1059,10 +2008,74 @@
       <c r="A18" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: You have a red lottery ticket showing ints a, b, and c, each of which is 0, 1, or 2. If they are all the value 2, the result is 10. Otherwise if they are all the same, the result is 5. Otherwise so long as both b and c are different from a, the result is 1. Otherwise the result is 0.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int redTicket(int a, int b, int c)
 {
+    if(a == b &amp;&amp; b == c)
+    {
+        if(a == 2)
+            return 10;
+    	return 5;
+    }
+    if( a!=b &amp;&amp; a != c)
+        return 1;
+    return 0;
+}
+##Solution 2 is:
+public int redTicket(int a, int b, int c)
+{
+    if (a == b &amp;&amp; b == c)
+    {
+        if (a == 2)
+        {
+            return 10;
+        }
+        else 
+        {
+            return 5;
+        }
+    }
+    else if (b != a &amp;&amp; c != a)
+    {
+        return 1;
+    }
+    else 
+    {
+        return 0;
+    }
+}
+##Solution 3 is:
+public int redTicket(int a, int b, int c)
+{
+    if(a == b &amp;&amp; b == c)
+	{
+		if(a == 2)
+			return 10;
+		return 5;
+	}
+	if(a != b &amp;&amp; a !=c)
+		return 1;
+	return 0;
+}
+##Solution 4 is:
+public int redTicket(int a, int b, int c)
+{
+    int result = 0;
     if (a == 2 &amp;&amp; b == 2 &amp;&amp; c == 2)
+        result = 10;
+    else if (a == b &amp;&amp; b == c)
+        result = 5;
+    else if (a != b &amp;&amp; a != c)
+        result = 1;
+    else
+        result = 0;
+    return result;
+}
+##Solution 5 is:
+public int redTicket(int a, int b, int c)
+{
+    if (a == 2 &amp;&amp; b == 2 &amp;&amp; c == 2)
     {
         return 10;
     }
@@ -1070,7 +2083,7 @@
     {
         return 5;
     }
-    else if (a != b &amp;&amp; a != c)
+    else if (b != a &amp;&amp; c != a)
     {
         return 1;
     }
@@ -1090,18 +2103,89 @@
       <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">Write two methods in Java that implements the following logic: Given 3 int values, a, b, and c, return their sum. However, if any of the values is a teen--in the range 13..19 inclusive--then that value counts as 0, except 15 and 16 do not count as teens. Write a separate helper method called fixTeen() that takes in an int value and returns that value fixed for the teen rule. In this way you avoid repeating the teen code 3 times (i.e. "decomposition").
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int noTeenSum(int a, int b, int c)
 {
 	return fixTeen(a) + fixTeen(b) + fixTeen(c);
 }
 public int fixTeen(int n)
 {
-    if (n == 13 || n == 14 || n &gt;= 17 &amp;&amp; n &lt;= 19)
+    if ((n&gt;=13 &amp;&amp; n&lt;15) || (n&gt;16 &amp;&amp; n&lt;=19))
     {
         n = 0;
     }
+    else
+    {
+     	n = n;   
+    }
     return n;
+}
+##Solution 2 is:
+public int noTeenSum(int a, int b, int c)
+{
+	int d = fixTeen(a);
+    int e = fixTeen(b);
+    int f = fixTeen(c);
+    return d + e + f;
+}
+public int fixTeen(int n)
+{
+    if (n &gt;= 13 &amp;&amp; n &lt;= 19)
+    {
+     	if (n == 15 || n == 16)
+            return n;
+        else
+            return 0;
+    }
+    else
+        return n;
+}
+##Solution 3 is:
+public int noTeenSum(int a, int b, int c)
+{
+	int res=0;
+	res=res+ fixTeen(a);
+	res=res+ fixTeen(b);
+	res=res+ fixTeen(c);
+	return res;
+}
+public int fixTeen(int n)
+{
+    if(n&gt;12 &amp;&amp; n&lt;20){
+		if(n==15 || n==16) {
+            return n;
+        }
+		return 0;
+    }
+	return n;
+}
+##Solution 4 is:
+public int noTeenSum(int a, int b, int c)
+{
+	return (fixTeen(a) + fixTeen(b) +fixTeen(c)); 
+}
+public int fixTeen(int n)
+{
+    if(n &lt; 13 || n &gt; 19 || n == 15 || n == 16)
+		return n;
+	return 0;
+}
+##Solution 5 is:
+public int noTeenSum(int a, int b, int c)
+{
+   return fixTeen(a) + fixTeen(b) + fixTeen(c);
+}
+public int fixTeen(int n)
+{
+    if (n &gt;= 13 &amp;&amp; n &lt;= 19 &amp;&amp; n != 15 &amp;&amp; n != 16)
+    {
+        return 0;
+    }
+    else
+    {
+        return n;
+    }
 }
 </t>
         </is>
@@ -1114,25 +2198,68 @@
       <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">Given a string, if the same 2-character substring appears at both its beginning and end, return the contents of the string without the 2-character substring at the beginning. For example, "HelloHe" yields "lloHe". Note that the 2-character substring at the beginning may overlap with the one at the end, so "Hi" yields "". If the two characters at the start and end of the string do not match each other, return the original string unchanged.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String without2(String str) 
 {
-    if (str.length() &gt; 1)
-    {
-    	int end = str.length();
-    	if (str.substring(0, 2).equals(str.substring(end - 2, end)))
-    	{
-    		return str.substring(2);
-    	}
-    	else
-    	{
-        	return str;
-    	}
-    }
+String toe = "";
+  if (str.length() &lt; 2 ) {
+    return str;
+  }
+  String front = str.substring(0,2); // first two substring 
+  for (int i = 0; i &lt; str.length(); i++) {
+    if (front.equals(str.substring(str.length()-2 ))) {
+      toe = toe + str.substring(2);
+      return toe;
+    }
+    else {
+      return str;
+    }
+  }
+  return "";
+}
+##Solution 2 is:
+public String without2(String str) 
+{
+    int len = str.length();
+    if (len &lt; 2)
+        return str;
+    else if (str.substring(0, 2).equals(str.substring(len - 2, len)))
+        return str.substring(2, len);
     else
-    {
         return str;
-    }
+}
+##Solution 3 is:
+public String without2(String str) 
+{
+    String answer = str;
+    if (str.length() &gt;= 2 &amp;&amp; (str.substring(0, 2).equals(str.substring(str.length() - 2))))
+    {
+        answer = str.substring(2, str.length());
+    }
+return answer;
+}
+##Solution 4 is:
+public String without2(String str) 
+{
+    if (str.length() &gt;= 2 &amp;&amp; str.substring(0, 2).
+        equals(str.substring(str.length() - 2))) 
+       {
+           return str.substring(2, str.length());
+       }
+       return str;
+}
+##Solution 5 is:
+public String without2(String str) 
+{
+    int length = str.length();
+    if (length &gt;= 2)
+        if (str.substring(0,2).equals(str.substring(length-2, length)))
+            return str.substring(2);
+        else
+            return str;
+    else
+            return str;
 }
 </t>
         </is>
@@ -1145,21 +2272,69 @@
       <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given a string, return a string made of its first 2 chars. If the string length is less than 2, use '@' for the missing chars.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String atFirst(String str)
 {
-    if (str.length() &gt; 1)
-    {
-    	return str.substring(0, 2);
+   int len = str.length();
+	if(len &gt;= 2)
+		return str.substring(0, 2);
+	else if(len == 1)
+		return (str.charAt(0)+"@");
+	else
+		return "@@";
+}
+##Solution 2 is:
+public String atFirst(String str)
+{
+    if (str.length() == 0) return "@@";
+    if (str.length() == 1) return str + "@";
+    return str.substring(0,2);
+}
+##Solution 3 is:
+public String atFirst(String str)
+{
+    String s;
+    if (str.length() == 0)
+    {
+        s = "@@";
     }
     else if (str.length() == 1)
     {
-        return str.substring(0, 1) + "@";
-    }
+        s = str +"@";
+    }   
     else
     {
+        s = str.substring(0, 2);
+    }
+    return s;
+}
+##Solution 4 is:
+public String atFirst(String str)
+{
+    if (str.length() == 1)
+    {
+        return (str.substring(0, 1) + "@");
+    }
+    else if (str.length() == 0)
+    {
         return "@@";
     }
+    else
+    {
+        return (str.substring(0, 2));
+    }
+}
+##Solution 5 is:
+public String atFirst(String str)
+{
+    int length = str.length();
+    if (length &gt;= 2)
+        return str.substring(0, 2);
+    else if (length == 1)
+        return str.charAt(0) + "@";
+    else
+        return "@@";
 }
 </t>
         </is>
@@ -1172,14 +2347,94 @@
       <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">A sandwich is two pieces of bread with something in between. Write a Java method that takes in a string str and returns the string that is between the first and last appearance of "bread" in str. Return the empty string "" if there are not two pieces of bread.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String getSandwich(String str)
 {
-    int first = str.indexOf("bread");
-    int last = str.lastIndexOf("bread");
-    if((last != -1 ) &amp;&amp; (first!=last))
-        return (str.substring(first+5,last)) ;
+    int i = str.indexOf("bread");
+    int l = str.lastIndexOf("bread");
+    if((l != -1) &amp;&amp; (i != l)){
+        return str.substring(i+5, l);
+    }else{
+        return "";
+    }
+}
+##Solution 2 is:
+public String getSandwich(String str)
+{
+    int len = str.length();
+	  String tmpString = "";
+  String finalString = "";
+	  int start = 0;
+	  int finish = 0;
+	  boolean found = false;
+	  if (len &lt;= 10)
+	    return "";
+	  for (int i = 0; i &lt; len - 4; i++) {
+	    tmpString = str.substring(i, i+5);
+	    if (tmpString.equals("bread") &amp;&amp; found == true)
+	      finish = i; 
+	    if (tmpString.equals("bread") &amp;&amp; found == false) {
+	      start = i+5;
+	      found = true;
+	    }
+	  }
+	  finalString = str.substring(start,finish);
+	  return finalString;
+}
+##Solution 3 is:
+public String getSandwich(String str)
+{
+    int first = -1;
+    int last = -1;
+    for(int i = 0; i &lt; str.length() - 5; i++) {
+        if(str.substring(i, i + 5).equals("bread")) {
+            first = i;
+            break;
+        }
+    }
+    for(int i = str.length() - 5; i &gt;= 0; i--) {
+        if(str.substring(i, i + 5).equals("bread")) {
+            last = i;
+            break;
+        }
+    }
+    if(first != -1 &amp;&amp; last != -1 &amp;&amp; first != last)
+        return str.substring(first + 5, last);
     return "";
+}
+##Solution 4 is:
+public String getSandwich(String str)
+{
+    int length = str.length();
+    int firstBread = str.indexOf('d');
+    int lastBread = str.lastIndexOf('b');
+    if (length &gt; 10)
+    {
+        if (firstBread == -1 || lastBread == -1)
+        {
+            return "";
+        }
+        else
+        {
+            return str.substring(firstBread + 1, lastBread);
+        }
+    }
+    else
+    {
+        return "";
+    }
+}
+##Solution 5 is:
+public String getSandwich(String str)
+{
+    int x = str.indexOf("bread", 0) + 5;
+    int y = str.lastIndexOf("bread");
+    if ((y - x) &lt; 0)
+    {
+        return "";
+    }
+    return str.substring(x, y);
 }
 </t>
         </is>
@@ -1192,7 +2447,8 @@
       <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">Given two strings, return true if either of the strings appears at the very end of the other string, ignoring upper/lower case differences (in other words, the computation should not be "case sensitive"). Note: str.toLowerCase() returns the lowercase version of a string.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean endOther(String a, String b)
 {
     int aLen = a.length();
@@ -1213,6 +2469,105 @@
 	}
 	return (end.equals(temp));
 }
+##Solution 2 is:
+public boolean endOther(String a, String b)
+{
+    a = a.toLowerCase();
+  	int aLen = a.length();
+  	b = b.toLowerCase();
+  	int bLen = b.length();
+  	if (aLen &lt; bLen) {
+    	String temp = b.substring(bLen - aLen, bLen);
+    if (temp.compareTo(a) == 0){
+      	return true;
+    }
+    else{
+      	return false;
+    }
+  } 
+    else {
+    	String temp = a.substring(aLen - bLen, aLen);
+    if (temp.compareTo(b) == 0){
+      	return true;
+    }
+    else{
+      	return false;
+    }
+  }
+}
+##Solution 3 is:
+public boolean endOther(String a, String b)
+{
+    a = a.toLowerCase();
+    b = b.toLowerCase();
+    if (a.length() &gt;= b.length()
+        &amp;&amp; a.substring(a.length() - b.length(), a.length()).equals(b))
+    {
+        return true;
+    }
+    else if (b.length() &gt;= a.length()
+             &amp;&amp; b.substring(b.length() - a.length(), b.length()).equals(a))
+    {
+        return true;
+    }
+    else
+    {
+        return false;
+    }
+}
+##Solution 4 is:
+public boolean endOther(String a, String b)
+{
+    int aLen = a.length();
+    int bLen = b.length();
+    a = a.toLowerCase();
+    b = b.toLowerCase();
+    if (aLen &lt; bLen)
+    {
+        String temp = b.substring(bLen - aLen, bLen);
+        if (temp.compareTo(a) == 0)
+        {
+            return true;
+        }
+        else 
+        {
+            return false;
+        }
+    }
+    else
+    {
+        String temp = a.substring(aLen - bLen, aLen);
+        if (temp.compareTo(b) == 0)
+        {
+            return true;
+        }
+        else
+        {
+            return false;
+        }
+    }
+}
+##Solution 5 is:
+public boolean endOther(String a, String b)
+{
+    int lengtha = a.length();
+    int lengthb = b.length();
+    String end;
+	String temp;
+	a = a.toLowerCase();
+	b = b.toLowerCase();
+	if (lengtha &gt;= lengthb)
+    {
+		end = a.substring(lengtha - lengthb);
+		temp = b;
+	}
+	else
+	{
+		end = b.substring(lengthb - lengtha);
+		temp = a;
+	}
+	return (end.equals(temp));
+}
 </t>
         </is>
       </c>
@@ -1224,27 +2579,111 @@
       <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that returns true if the given string str contains an occurrence of the substring "xyz" where "xyz" is not directly preceded by a period ("."). For example, "xxyz" counts, while "x.xyz" does not.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean xyzThere(String str)
 {
-    int occ = str.indexOf("xyz");
-    int occ2 = str.lastIndexOf("xyz");
-    if (occ == 0)
+    int index = str.indexOf(".xyz");
+    if(index &gt;= 0) {
+        return xyzThere(str.substring(0, index)) || xyzThere(str.substring(index + 4));
+    } else return (str.contains("xyz"));
+}
+##Solution 2 is:
+public boolean xyzThere(String str)
+{
+        int j = 0;
+        int k = 0;
+        for (int i = 1; i &lt;= str.length() - 5; i++)
+        {
+            String a = str.substring(i + 1, i + 1);
+            String b = str.substring(i + 2, i + 2);
+            String c = str.substring(i + 3, i + 3);
+            String d = str.substring(i, i);
+            if (a == "x" &amp;&amp; b == "y" &amp;&amp; c == "z")
+            {
+                if (d == ".")
+                {
+                    k = 1;
+                }
+                else
+                {
+                   j = 1; 
+                }
+            }
+        }
+        if (j == 1)
+        {
+            return true;
+        }
+        else if (str.startsWith("xyz"))
+        {
+            return true;
+        }
+        else if (str.endsWith(".xyz"))
+        {
+            return false;
+        }
+        else if (str.endsWith("xyz"))
+        {
+            return true;
+        }
+        else 
+        {
+            return false;   
+        }
+}
+##Solution 3 is:
+public Boolean xyzThere(String str) {
+  int len = str.length();
+  String xyz = "xyz";
+  Boolean match = false;
+  if (len &lt; 3)
+    return false;
+  for (int i = 0; i &lt; len - 2; i ++) {
+    String temp = str.substring(i, i+3); 
+    if (temp.compareTo(xyz) == 0 &amp;&amp; i == 0)
+      match = true;
+    else if(temp.compareTo(xyz) == 0 &amp;&amp; str.charAt(i-1) != 46)
+      match = true;
+  }  
+  return match;
+}
+##Solution 4 is:
+public boolean xyzThere(String str)
+{
+    for (int i = 0; i &lt; str.length(); i++)
+    {
+    	if (str.charAt(i) == 'x' &amp;&amp; i != 0)
+        {
+        	if (str.charAt(i-1) != '.' &amp;&amp; (i+2) &lt; str.length())
+            {
+            	if (str.charAt(i+1) == 'y' &amp;&amp; str.charAt(i+2) == 'z')
+                {
+                	return true;
+                }
+            }
+        }
+        else if (str.charAt(i) == 'x' &amp;&amp; (i+2) &lt; str.length())
+        {    
+			if (str.charAt(i+1) == 'y' &amp;&amp; str.charAt(i+2) == 'z')
+            {
+				return true;
+			}
+        }
+    }
+    return false;
+}
+##Solution 5 is:
+public boolean xyzThere(String str)
+{
+    String sub = str.substring(0);
+    if (str.startsWith("xyz"))
     {
         return true;
     }
-    else if (occ &gt; 0)
-    {
-        String per = str.substring(occ - 1, occ);
-        String per2 = str.substring(occ2 - 1, occ2);
-        if (per.equals(".") &amp;&amp; per2.equals("."))
-        {
-            return false;
-        }
-        else
-        {
-        	return true;
-        }
+    else if (str.endsWith("xyz") &amp;&amp; !str.endsWith(".xyz"))
+    {
+        return true;
     }
     else
     {
@@ -1262,43 +2701,69 @@
       <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve">Return true if the given string contains a "bob" string, but where the middle 'o' character can be any character.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean bobThere(String str)
 {
-    int b = str.indexOf("b");
-    int b2 = str.lastIndexOf("b");
-    if (b2 &lt; 2)
-    {
-        return false;
-    }
-    else if (b &gt;= b2)
-    {
-        String ch = str.substring(b + 2, b + 3);
-        if (ch.equals("b"))
-    	{
-        	return true;
-    	}
-    	else
-    	{
-        	return false;
-    	}
-    }
-    else if (b &lt; b2)
-    {
-   		String ch2 = str.substring(b2 - 2, b2 - 1);
-    	if (ch2.equals("b"))
-    	{
-        	return true;
-    	}	
-    	else
-    	{
-        	return false;
-    	}
-    }
-    else
-    {
-        return false;
-    }
+	int len = str.length() - 2;
+	for(int i = 0; i &lt; len; i++)
+	{
+		if(str.charAt(i) == 'b' &amp;&amp; str.charAt(i+2) == 'b')
+			return true;
+	}
+	return false;
+}
+##Solution 2 is:
+public boolean bobThere(String str)
+{
+    int a = 0;
+    for (int i= 0; i &lt; str.length() - 2; i ++)
+    {
+    	if (str.charAt(i) == 'b' &amp;&amp; str.charAt(i + 2) == 'b')
+        {
+        	a = 1;
+            break;
+        }
+    }
+    return(a == 1);
+}
+##Solution 3 is:
+public boolean bobThere(String str)
+{
+    for (int i = 0; i &lt; str.length()-2; i++) {
+    if (str.charAt(i) == 'b' &amp;&amp; str.charAt(i+2) == 'b') {
+      return true;
+    }
+  }
+  return false;
+}
+##Solution 4 is:
+public boolean bobThere(String str)
+{
+	int length = str.length() - 2;
+	for(int i = 0; i &lt; length; i++)
+	{
+		if(str.charAt(i) == 'b' &amp;&amp; str.charAt(i+2) == 'b')
+			return true;
+	}
+	return false;
+}
+##Solution 5 is:
+public boolean bobThere(String str)
+{
+    //int firstB = str.indexOf("b");
+   // int secondB = str.lastIndexOf("b");
+    //if (secondB == firstB + 2)
+    //    return true;
+   // return false;
+    for (int n = 0; n &lt; str.length() - 2; n++)
+    {
+        if (str.charAt(n) == 'b' &amp;&amp; str.charAt(n + 2) == 'b')
+        {
+            return true;
+        }
+    }//end for loop
+    return false;
 }
 </t>
         </is>
@@ -1311,31 +2776,87 @@
       <c r="A26" t="inlineStr">
         <is>
           <t xml:space="preserve">We'll say that a string is xy-balanced if for all the 'x' characterss in the string, there exists a 'y' character somewhere later in the string. So "xxy" is balanced, but "xyx" is not. One 'y' can balance multiple 'x's. Return true if the given string is xy-balanced.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean xyBalance(String str)
 {
-    int x = str.indexOf("x");
-    int xy = str.indexOf("xy");
-    int xxy = str.indexOf("xxy");
-    int xbby = str.indexOf("xbby");
-    int lastx = str.lastIndexOf("x");
-    int length = str.length();
-    if (x == -1)
-    {
-        return true;
-    }
-    else if (lastx == length - 1)
-    {
-        return false;
-    }    
-    else if (xy &gt;= 0 || xxy &gt;= 0 || xbby &gt;= 0)
-    {
-        return true;
+    int len = str.length() - 1;
+	char ch;
+	for(int i = len; i &gt;= 0; i--)
+	{
+		ch = str.charAt(i);
+		if(ch == 'x')
+			return false;
+		else if(ch == 'y')
+			return true;
+	}
+	return true;  
+}
+##Solution 2 is:
+public boolean xyBalance(String str)
+{
+    boolean y = false;
+    for(int i = str.length() - 1; i &gt;= 0; i--) {
+        if(str.charAt(i) == 'y')
+            y = true;
+        if(str.charAt(i) == 'x' &amp;&amp; !y)
+            return false;
+    }
+    return true;
+}
+##Solution 3 is:
+public boolean xyBalance(String str)
+{
+    int len = str.length() - 1;
+	char ch;
+	for(int i = len; i &gt;= 0; i--)
+	{
+		ch = str.charAt(i);
+		if(ch == 'x')
+			return false;
+		else if(ch == 'y')
+			return true;
+	}
+	return true;  
+}
+##Solution 4 is:
+public boolean xyBalance(String str)
+{
+    if (str.lastIndexOf("x")!=-1)
+    {
+    	for (int i=str.length()-1; str.length()&gt;=0; i--)
+    	{
+        	if (str.charAt(i)=='x')
+        	{
+            	return false;
+        	}
+        	else if (str.charAt(i)=='y')
+        	{
+            	return true;
+        	}
+    	}
+    }
+    return true;
+}
+##Solution 5 is:
+public boolean xyBalance(String str)
+{
+    if((str.lastIndexOf("y") &gt; str.lastIndexOf("x")))
+    {
+        return true;   
+    }
+    else if (str.lastIndexOf("y") == -1 &amp;&amp; str.lastIndexOf("x") == -1)
+    {
+     	return true;   
     }
     else
     {
-        return false;
-    }
+     	return false;
+    }
+    /*for (int i = str.length(); i &gt; 0; i--)
+    {
+        if ()
+    }8*/
 }
 </t>
         </is>
@@ -1348,19 +2869,112 @@
       <c r="A27" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that counts the number of times the string "code" appears anywhere in the given string str, except that we'll accept any letter in place of the 'd', so for example, "cope" and "cooe" count.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int countCode(String str)
 {
-    int cc = 0;
-    for (int i = 0; i &lt; str.length() - 3; i++)
-    {
-        if (str.substring(i, i + 2).equals("co") &amp;&amp; 
-            str.substring(i + 3, i + 4).equals("e"))
-        {
-            cc++;
-        }
-    }
-    return cc;
+    int count = 0;
+	int integer = 0;
+	int length = str.length()-3;
+	while(integer &lt;  length)
+	{
+		if(str.charAt(integer) == 'c' &amp;&amp; str.charAt(integer+1) == 'o' &amp;&amp; str.charAt(integer+3) == 'e')
+		{
+			count++;
+			integer += 4;
+		}
+		else
+			integer++;
+	}
+	return count;
+}
+##Solution 2 is:
+public int countCode(String str)
+{
+    int stringLength = str.length();
+    int numberOfCode = 0;
+    if (stringLength &gt;= 4)
+    {
+        for (int i = 0; i &lt; stringLength - 3; i++)
+        {
+            boolean findCO = str.startsWith("co", i);
+            boolean findE = str.startsWith("e", i + 3);
+            if (findCO &amp;&amp; findE)
+            {
+                numberOfCode = numberOfCode + 1;
+            }
+        }
+        return numberOfCode;
+    }
+    else
+    {
+        return numberOfCode;
+    }
+}
+##Solution 3 is:
+int count = 0;
+public int countCode(String str)
+{
+    if (str.length() &gt;= 4)
+    {
+    	for (int i = 0; i &lt; str.length() - 3; i++)
+    	{
+     		if (str.substring(i, i + 2).equals("co") &amp;&amp;
+               str.charAt(i + 3) == 'e')
+            {
+                count++;
+            }
+    	}
+    }
+    return count;
+}
+##Solution 4 is:
+public int countCode(String str)
+{
+     int count = 0;
+        for ( int i = 0; i &lt; str.length() - 3; i++ )
+        {
+            if ( "co".equals( str.substring( i, i + 2 ) ) )
+            {
+                if ( str.charAt( i + 3 ) == 'e' )
+                {
+                    count++;
+                }
+            }
+        }
+        return count;
+}
+##Solution 5 is:
+public int countCode(String str)
+{
+    int check = 0;
+	while (str.length() &gt; 1)
+    {
+        int index = str.indexOf("co");
+        String checkWord;
+        if (index != -1)
+        {
+            str = str.substring(index + 2);
+            index = str.indexOf("e");
+            if (index != -1)
+            {
+                checkWord = str.substring(0, index);
+                if (checkWord.length() == 1)
+                {
+                	check += 1;
+                }
+            }
+            else
+            {
+                str = "";
+            }
+        }
+        else
+        {
+            str = "";
+        }
+    }
+    return check;
 }
 </t>
         </is>
@@ -1373,43 +2987,99 @@
       <c r="A28" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given a string str and a non-empty word, return a version of the original string where all chars have been replaced by pluses (+), except for appearances of the word which are preserved unchanged.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String plusOut(String str, String word)
 {
-    String string = new String();
-    int length = word.length();
-    for (int i = 0; i &lt; str.length() - length; i++)
-    {
-        if (str.substring(i, i + length).equals(word))
-        {
-            string = string + word;
-            i = i + length - 1;
-        }
-        else
-        {
-            string = string + "+";
-        }
-    }
-    if (str.substring(str.length() - length, 			str.length()).equals(word))
-    {
-        return string + word;
-    }
-    else if (str.substring(str.length() - length - 1, 			str.length()).equals(word + "Z"))
-    {
-        return string + "+";
-    }
-    else if (length == 1)
-    {
-    	return string + "+";
-    }
-    else if (length == 2)
-    {
-    	return string + "++";
-    }
-    else
-    {
-    	return string + "+++";
-    }
+    int i = 0; 
+    String str2 = "";
+    while (i &lt; str.length() - word.length()+1) 
+        if (!str.substring(i,i+word.length()).equals(word)) {
+            str2 += "+";
+            i++;
+        }
+        else {
+            str2 += word;
+            i += word.length(); 
+        }
+    if (i &lt; str.length() &amp;&amp; !str.substring(i).equals(word.substring(1))) {
+        for (int j = 0; j &lt; word.length()-1; j++) str2 += "+";
+    }
+    return str2;
+}
+##Solution 2 is:
+public String plusOut(String str, String word)
+{
+    int i = 0; 
+    String str2 = "";
+    while (i &lt; str.length() - word.length()+1) 
+        if (!str.substring(i,i+word.length()).equals(word)) {
+            str2 += "+";
+            i++;
+        }
+        else {
+            str2 += word;
+            i += word.length();
+        }
+    if (i &lt; str.length() &amp;&amp; !str.substring(i).equals(word.substring(1))) {
+        for (int j = 0; j &lt; word.length()-1; j++) str2 += "+";
+    }
+    return str2;
+}
+##Solution 3 is:
+public String plusOut(String str, String word) {
+String res="";
+int i=0;
+while(i&lt;str.length()){
+if(str.substring(i).startsWith(word)){
+res=res+word;
+i=i+word.length();
+}
+else {
+res=res+"+";
+i++;
+}
+}
+return res;
+}
+##Solution 4 is:
+public String plusOut(String str, String word)
+{
+    int strLength = str.length();
+    int wordLength = word.length();
+    int position = str.indexOf(word);
+    int i = 0;
+    StringBuilder strbuild = new StringBuilder(strLength);
+    while(position != -1)
+    {
+     	while ( i &lt; position)
+        {
+         	strbuild.append('+');
+            i++;
+        }
+        strbuild.append(word);
+        i = position + wordLength;
+        position = str.indexOf(word, i);
+    }
+    for(; i&lt;strLength; i++)
+        strbuild.append('+');
+    return strbuild.toString();
+}
+##Solution 5 is:
+public String plusOut(String str, String word)
+{
+    String a = "";
+        for (int i =0;i &lt; str.length(); i ++){
+        if (str.startsWith(word, i))
+        {
+        	a = a + word;
+            i = i + word.length() - 1;
+        }else
+        {
+        	a = a + "+";
+        }
+    }
+    return a;
 }
 </t>
         </is>
@@ -1422,18 +3092,57 @@
       <c r="A29" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given a string and an int n, return a string made of n repetitions of the last n characters of the string. You may assume that n is between 0 and the length of the string, inclusive.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String repeatEnd(String str, int n)
 {
-    int length = str.length();
-    int i = 1;
-    String rep = str.substring(length - n, length);
-    while (i &lt; n)
-    {
-        rep = rep + str.substring(length - n, length);
-        i++;
-    }
-    return rep;
+    String value = "";
+    int k = str.length();
+    for (int i = 0; i &lt; n; i++)
+    {
+        value = value + str.substring(k - n, k);
+    }
+    return value;
+}
+##Solution 2 is:
+public String repeatEnd(String str, int n)
+{
+    String end = str.substring(str.length() - n);
+    String ret = "";
+    for(int q = 0; q &lt; n; q++)
+    {
+    ret = ret + end;
+    }
+    return ret;
+}
+##Solution 3 is:
+public String repeatEnd(String str, int n)
+{
+    StringBuilder stbuild = new StringBuilder(n*n);
+	String last = str.substring(str.length()-n);
+	for(int i = 0; i &lt; n; i++)
+		stbuild.append(last);
+	return stbuild.toString();
+}
+##Solution 4 is:
+public String repeatEnd(String str, int n)
+{
+    String end;
+String result = "";
+end = str.substring(str.length() - n, str.length());
+for(int i = 0; i &lt; n; i++) {
+result += end;
+}
+return result;
+}
+##Solution 5 is:
+public String repeatEnd(String str, int n)
+{
+	StringBuilder stbuild = new StringBuilder(n*n);
+	String last = str.substring(str.length()-n);
+	for(int i = 0; i &lt; n; i++)
+		stbuild.append(last);
+	return stbuild.toString();
 }
 </t>
         </is>
@@ -1446,27 +3155,110 @@
       <c r="A30" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Given two strings, a and b, create a bigger string made of the first character of a, the first character of b, the second character of a, the second character of b, and so on. Any leftover characters go at the end of the result.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String mixString(String a, String b)
 {
-    int minl = Math.min(a.length(), b.length());
-    String string = new String();
-    for (int i = 0;  i &lt; minl; i++)
-    {
-        string = string + a.substring(i, i + 1) + b.substring(i, i + 1);
-    }
-    if (a.length() == b.length())
-    {
-        return string;
-    }
-    else if (a.length() &gt; minl)
-    {
-        return string + a.substring(minl, a.length());
+    String word = "";
+    int lenA = a.length();
+    int lenB = b.length();
+    if (lenA &gt; lenB)
+    {
+        for (int i = 0; i &lt; lenB; i++)
+        {
+            word += a.substring(i, i+1) + b.substring(i, i+1);
+        }
+        word += a.substring(lenB);
     }
     else
     {
-        return string + b.substring(minl, b.length());
-    }
+        for (int i = 0; i &lt; lenA; i++)
+        {
+            word += a.substring(i, i + 1) + b.substring(i, i + 1);
+        }
+        word += b.substring(lenA);
+    }
+    return word;
+}
+##Solution 2 is:
+public String mixString(String a, String b)
+{
+    int aLength = a.length();
+    int bLength = b.length();
+    int i = 0;
+    StringBuilder strbuild = new StringBuilder(aLength+bLength);
+    for(; i&lt;aLength &amp;&amp; i&lt;bLength; i++)
+    {
+     	strbuild.append(a.charAt(i));
+        strbuild.append(b.charAt(i));
+    }
+    for (; i&lt;aLength; i++)
+    {
+     strbuild.append(a.charAt(i));   
+    }
+    for(; i&lt;bLength; i++)
+    {
+     strbuild.append(b.charAt(i));   
+    }
+    return strbuild.toString();
+}
+##Solution 3 is:
+public String mixString(String a, String b)
+{
+    int aLength = a.length();
+	int bLength = b.length();
+	int i = 0;
+	StringBuilder newString = new StringBuilder(aLength + bLength);
+	for (;i &lt; aLength &amp;&amp; i &lt; bLength; i++)
+	{
+		newString.append(a.charAt(i));
+		newString.append(b.charAt(i));
+	}
+	for (;i &lt; aLength; i++)
+    {
+		newString.append(a.charAt(i));
+    }
+	for (;i &lt; bLength; i++)
+    {
+		newString.append(b.charAt(i));
+    }
+	return newString.toString();
+}
+##Solution 4 is:
+public String mixString(String a, String b)
+{
+    int aLen = a.length();
+	int bLen = b.length();
+	int i = 0;
+	StringBuilder stbuild = new StringBuilder(aLen+bLen);
+	for(; i &lt; aLen &amp;&amp; i &lt; bLen; i++)
+	{
+		stbuild.append(a.charAt(i));
+		stbuild.append(b.charAt(i));
+	}
+	// only 1 for loop will actually run
+	for(; i &lt; aLen; i++)
+		stbuild.append(a.charAt(i));
+	for(; i &lt; bLen; i++)
+		stbuild.append(b.charAt(i));
+	return stbuild.toString();
+}
+##Solution 5 is:
+public String mixString(String a, String b)
+{
+      String res="";
+    int i;
+    for(i=0;i&lt;a.length() &amp;&amp; i&lt;b.length();i++)
+     {
+            res=res+a.charAt(i);
+            res=res+b.charAt(i);
+     }
+    if(a.length()&lt;b.length())
+    {
+            res=res+b.substring(i);
+    }
+    else res=res+a.substring(i);
+    return res;
 }
 </t>
         </is>
@@ -1479,37 +3271,118 @@
       <c r="A31" t="inlineStr">
         <is>
           <t xml:space="preserve">Given a string str, find all places where a three-letter combination starting with "z" and ending with "p" occurs. Return a string where for all such three-letter sequences, the middle letter has been removed. For example, a string like "zipXzap" would produce a result of "zpXzp".
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String zipZap(String str)
 {
-    String string = new String();
-    if (str.length() &gt;= 3)
-    {
-    	for (int i = 0;  i &lt; str.length() - 2; i++)
-    	{
-        	if (str.substring(i, i + 1).equals("z") &amp;&amp; 			str.substring(i + 2, i + 3).equals("p"))
-     	   {
-        	    string = string + "zp";
-            	i = i + 2;
-        	}
-        	else
-        	{
-            	string = string + str.substring(i, i + 1);
-        	}
-    	}
-    	if (str.substring(str.length() - 3, str.length() - 2).equals("z"))
-    	{
-        	return string;
-    	}
-    	else
-    	{
-    		return string + str.substring(str.length() - 2, str.length());
-    	}
-    }
-    else
-    {
+    int len = str.length();
+    int len2 = str.length() - 2;
+    int i = 0;
+    char c;
+    StringBuilder newStr = new StringBuilder(len);
+    while (i &lt; len)
+    {
+    	c = str.charAt(i);
+        if (c == 'z' &amp;&amp; i &lt; len2 &amp;&amp; str.charAt(i+2) == 'p')
+        {
+        	newStr.append("zp");
+            i = i + 3;
+        }
+        else
+        {
+        	newStr.append(c);
+        	i++;
+        }
+    }
+    return newStr.toString();
+}
+##Solution 2 is:
+public String zipZap(String str)
+{
+    String s = "";
+    int x = 0;
+    int y = 0;
+    boolean ye = false;
+    if (str.length() &lt; 3) {
         return str;
     }
+    else {
+        for (int i = 0; i &lt; str.length() - 2; i++) {
+            if (str.charAt(i) == 'z' &amp;&amp; str.charAt(i + 2) == 'p') {
+                ye = true;
+                x++;
+            }
+        }
+    	while (s.length() != str.length() - x &amp;&amp; y &lt; str.length()) {
+            if (str.charAt(y) == 'z' &amp;&amp; str.charAt(y + 2) == 'p' &amp;&amp; ye) {
+                s = s + "zp";
+                y = y + 2;
+            }
+            else {
+                s = s + str.charAt(y);
+            }
+            y++;
+        }
+    }
+    return s;
+}
+##Solution 3 is:
+public String zipZap(String str)
+{
+    int i = 0;
+   while (i &lt; str.length() - 2) 
+    {
+    if (str.charAt(i) == 'z' &amp;&amp; str.charAt(i + 2) == 'p')
+    {
+        str = str.substring(0, i+1) + str.substring(i+2);
+    }
+       i++;
+   }
+       return str;
+}
+##Solution 4 is:
+public String zipZap(String str)
+{
+    int i = 0;
+    String combo = str, empty = "";
+   	int len = combo.length();
+    while(i &lt; len - 2)
+    {
+		if(combo.charAt(i) == 'z' &amp;&amp; combo.charAt(i + 2) == 'p')
+        {
+			empty = empty + combo.substring(0, i + 1);
+			combo = combo.substring(i + 2);
+			len = combo.length();
+			i = 0;
+		}
+		i++;
+	}
+empty = empty + combo;
+return empty;
+}
+##Solution 5 is:
+public String zipZap(String str)
+{
+ int len = str.length();
+	int lim = len - 2;
+	int i = 0;
+	char ch;
+	StringBuilder stbuild = new StringBuilder(len);
+	while(i &lt; len)
+	{
+		ch = str.charAt(i);
+		if(ch == 'z' &amp;&amp; i &lt; lim &amp;&amp; str.charAt(i+2) == 'p')
+		{
+			stbuild.append("zp");
+			i += 3;
+		}
+		else
+		{
+			stbuild.append(ch);
+			i++;
+		}
+	}
+	return stbuild.toString();
 }
 </t>
         </is>
@@ -1522,7 +3395,35 @@
       <c r="A32" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an array containing three ints, return the sum of all the elements.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
+public int sum3(int[] nums)
+{
+    return (nums[0] + nums[1] + nums[2]);	
+}
+##Solution 2 is:
+public int sum3(int[] nums)
+{
+    int sum = 0;
+    sum = nums[0] +nums[1]+nums[2];
+    return sum;
+}
+##Solution 3 is:
+public int sum3(int[] nums)
+{
+    return nums[0] + nums[1] + nums[2];
+}
+##Solution 4 is:
+public int sum3(int[] nums)
+{
+    int total = 0;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        total += nums[i];
+    }
+    return total;
+}
+##Solution 5 is:
 public int sum3(int[] nums)
 {
     return nums[0] + nums[1] + nums[2];
@@ -1538,24 +3439,92 @@
       <c r="A33" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an int array of any length, return a new array of its first 2 elements. If the array is smaller than length 2, use whatever elements are present.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] frontPiece(int[] nums)
 {
-    int[] two;
-	if(nums.length &gt;= 2)
-	{
-		two = new int[2];
-		two[0] = nums[0];
-		two[1] = nums[1];
-	}
-	else if(nums.length == 1)
-	{
-		two = new int[1];
-		two[0] = nums[0];
-	}
-	else
-		two = new int[0];
-	return two;
+    // make new array first
+    if ( nums.length &lt; 2) {
+        return nums;
+    }
+    int[] toes = { nums[0], nums[1] };
+    return toes;
+}
+##Solution 2 is:
+public int[] frontPiece(int[] nums)
+{
+    int[] newNums;
+    if (nums.length &gt;= 2)
+    {
+        newNums = new int[2];
+     	newNums[0] = nums[0];
+        newNums[1] = nums[1];
+    }
+    else if (nums.length == 1)
+    {
+     	newNums = new int[1];
+        newNums[0] = nums[0];
+    }
+    else
+    {
+     	newNums = new int[0];   
+    }
+    return newNums;
+}
+##Solution 3 is:
+public int[] frontPiece(int[] nums)
+{
+    int [] start;
+    if (nums.length &gt;= 2)
+    {
+        start = new int [2];
+        start [0] = nums [0];
+    	start [1] = nums [1];
+    }
+    else if (nums.length == 1)
+    {
+        start = new int [1];
+    	start [0] = nums [0];
+    }
+    else 
+    {
+        start = new int [0];
+    }
+    return start;
+}
+##Solution 4 is:
+public int[] frontPiece(int[] nums)
+{
+    if (nums.length &gt;= 2)
+    {
+    return new int[] {nums[0], nums[1]};
+    }
+    else if (nums.length == 1)
+    {
+       return new int[] {nums[0]};
+    }
+    else
+    {
+        return new int[0];
+    }
+}
+##Solution 5 is:
+public int[] frontPiece(int[] nums)
+{
+    if (nums.length &lt; 2)
+    {
+        int[] newNums = new int[nums.length];
+        for (int i = 0; i &lt; nums.length; i++)
+            newNums[i] = nums[i];
+        return newNums;
+    }
+    else
+    {
+        int[] newNums = new int[2];
+    	for (int i = 0; i &lt; 2; i++)
+            newNums[i] = nums[i];
+        return newNums;
+    }
 }
 </t>
         </is>
@@ -1568,20 +3537,63 @@
       <c r="A34" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that takes an int array as its parameter and returns the number of even ints it contains. Note: the % "mod" operator computes the remainder, e.g. 5 % 2 is 1.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int countEvens(int[] nums)
 {
-    int i = 0;
+    int total = nums.length;
+    for(int i=0;i&lt;nums.length;i++)
+    	total -= nums[i]%2;
+    return total;
+}
+##Solution 2 is:
+public int countEvens(int[] nums)
+{
     int count = 0;
-    while (i &lt; nums.length)
-    {
-    	if (nums[i] % 2 == 0)
-    	{
+    int its = nums.length - 1;
+    for (int i = 0; i &lt;= its; i++) {
+        if (nums[i] % 2 == 0) {
             count++;
         }
-        i++;
     }
     return count;
+}
+##Solution 3 is:
+public int countEvens(int[] nums)
+{
+    int count = 0;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        if (nums[i] % 2 == 0)
+        {
+            count++;
+        }
+    }
+    return count;
+}
+##Solution 4 is:
+public int countEvens(int[] nums)
+{
+    int even = 0;
+    for (int i = 0; i &lt; nums.length; i++) {
+        if (nums[i] % 2 == 0) {
+            even += 1;
+        }
+    }
+    return even;
+}
+##Solution 5 is:
+public int countEvens(int[] nums)
+{
+    int evens = 0;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        if(nums[i] % 2 == 0)
+        {
+            evens++;
+        }
+    }
+    return evens;
 }
 </t>
         </is>
@@ -1594,22 +3606,66 @@
       <c r="A35" t="inlineStr">
         <is>
           <t xml:space="preserve">We'll say that a value is "everywhere" in an array if for every pair of adjacent elements in the array, at least one of the pair is that value. Return true if the given value is everywhere in the array.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean isEverywhere(int[] nums, int val)
 {
-    int a = 0;
+    for(int i = 0; i &lt; nums.length-1; i++)
+	{
+		if(nums[i] != val &amp;&amp; nums[i+1] != val)
+			return false;
+	}  
+	return true;
+}
+##Solution 2 is:
+public boolean isEverywhere(int[] nums, int val)
+{
+    for (int i = 1; i &lt; nums.length; i++)
+    {
+    	if (nums[i - 1] != val &amp;&amp; nums[i] != val)
+            return false;
+    }
+    return true;
+}
+##Solution 3 is:
+public boolean isEverywhere(int[] nums, int val)
+{
+    int count = 0;
     for (int i = 0; i &lt; nums.length - 1; i++)
     {
-        if (nums[i] == val || nums[i + 1] == val)
-        {
-            a = a + a;
-        }
-        else
-        {
-            a = a + 1;
-        }
-    }
-    return a == 0;
+        int a = nums[i];
+        int b = nums[i + 1];
+        if (a == val || b == val)
+        {
+            count++;
+        }
+    }
+    if (nums.length == 0)
+    {
+        return true;
+    }
+    return count == nums.length - 1;
+}
+##Solution 4 is:
+public boolean isEverywhere(int[] nums, int val)
+{
+    for (int i = 0; i &lt; nums.length-1; i++)
+	{
+		if (nums[i] != val &amp;&amp; nums[i+1] != val)
+			return false;
+	}  
+	return true;
+}
+##Solution 5 is:
+public boolean isEverywhere(int[] nums, int val)
+{
+	boolean result = true;
+	for (int i = 0; i &lt;=nums.length-2;i++)
+	{
+		if ( nums[i] != val &amp;&amp; nums[i+1] != val)
+			result = false;
+	}
+  	return result;
 }
 </t>
         </is>
@@ -1622,36 +3678,100 @@
       <c r="A36" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that takes an array and returns the sum of the numbers in the array, or 0 if the array is empty. Except the number 13 is very unlucky, so it does not count any 13, or any number that immediately follows a 13.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int sum13(int[] nums)
 {
-    int sum = 0;
+    int count = 0;
+    if	(nums.length == 0)
+    {
+        return 0;
+    }
+    for	(int i = 0; i &lt; nums.length - 1; i++)
+    {
+        if (nums[i] == 13)
+        {
+            nums[i] = 0;
+            nums[i+1] = 0;
+            if (nums[i+1] == 13 &amp;&amp; i &lt; nums.length - 2)
+            {
+                nums[i + 2] = 0;
+            }
+        }
+        count = count + nums[i];
+    }
+    if (nums[nums.length - 1] != 13)
+    {
+        count = count + nums[nums.length - 1];
+    }
+    return count;
+}
+##Solution 2 is:
+public int sum13(int[] nums)
+{
+    int s = 0;
+    for(int i = 0; i &lt; nums.length; i++)
+        {
+            if(nums[i] == 13)
+                i++;
+            else
+                s = s + nums[i];
+        }
+        return s;
+}
+##Solution 3 is:
+public int sum13(int[] nums)
+{
+    int x = 0;
     for (int i = 0; i &lt; nums.length; i++)
     {
-        if (i &lt; nums.length)
-        {
-            if (nums[i] == 13)
-        	{
-            	i++;
-        	}
+        if (nums[i] != 13)
+        {
+            x += nums[i];
+        }
+        else
+        {
+            if (i &lt; nums.length)
+            {
+                i ++;
+            }
             else
             {
-                sum = sum + nums[i];
+                i = nums.length;
             }
         }
+    }
+    return x;
+}
+##Solution 4 is:
+public int sum13(int[] nums)
+{
+    int sum = 0;
+	for(int i = 0; i &lt; nums.length; i++)
+	{
+		if(nums[i] == 13)
+        {
+			i++;
+        }
+		else
+        {
+			sum += nums[i];
+        }
+	}
+	return sum;
+}
+##Solution 5 is:
+public int sum13(int[] nums)
+{
+     int sum = 0;
+ for (int i=0;i&lt;nums.length;i++)
+      {
+         if (nums[i] == 13)
+          i++;
         else
-        {
-            if (nums[i] == 13)
-        	{
-            	sum = sum + 0;
-        	}
-            else
-            {
-                sum = sum + nums[i];
-            }
-        }
-    }
-    return sum;
+          sum += nums[i];
+      }
+  return sum ;
 }
 </t>
         </is>
@@ -1664,33 +3784,76 @@
       <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an array of ints, return true if the array contains two 7s next to each other, or there are two 7s separated by one element, such as with {7, 1, 7}. Otherwise, return false.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean has77(int[] nums)
 {
-    int blob = 0;
-    for (int i = 0; i &lt; nums.length - 1; i++)
-    {
-        if (i &lt; nums.length - 2)
-        {
-            if (nums[i] == nums[i + 1] &amp;&amp; nums[i] == 7)
-        	{
-            	blob = blob + 100;
-        	}
-            if (nums[i] == nums[i + 2] &amp;&amp; nums[i] == 7)
-            {
-                blob = blob + 100;
+    for (int i = 0; i &lt;= nums.length - 2; i++) 
+    {
+            if (nums[i] == 7 &amp;&amp; nums[i + 1] == 7) {
+                return true;
             }
-        }   
-        else if (nums[i] == nums[i + 1] &amp;&amp; nums[i] == 7)
-        {
-            blob = blob + 100;
-        }
-        else
-        {
-            blob = blob + 1;
-        }
-    }
-    return blob &gt;= 100;
+            if (i &lt; nums.length - 2 &amp;&amp; (nums[i] == 7 &amp;&amp; nums[i + 	2] == 7)) {
+                return true;
+            }
+    }
+    return false;
+}
+##Solution 2 is:
+public boolean has77(int[] nums)
+{
+    for(int i = 0; i &lt; nums.length - 1; i++)
+  {
+  	if(nums[i] == 7)
+  	{
+			if(nums[i+1] == 7)
+				return true;
+			else if(i &lt; nums.length - 2 &amp;&amp; nums[i+2] == 7)
+				return true;
+		}
+	}
+	return false;
+}
+##Solution 3 is:
+public boolean has77(int[] nums)
+{
+    for(int i = 0; i &lt; nums.length - 1; i++) {
+        if(nums[i] == 7 &amp;&amp; nums[i+1] == 7)
+            return true;
+        if(i &lt;= nums.length - 3 &amp;&amp; nums[i] == 7 &amp;&amp; nums[i+2] == 7)
+            return true;
+    }
+    return false;
+}
+##Solution 4 is:
+public boolean has77(int[] nums)
+{
+    for (int i = 0; i &lt; nums.length -1 ; i++)
+    {
+        if (nums[i] == 7)
+        {
+            if (nums[i+1] == 7)
+                return true;
+            else if (i &lt; nums.length -2 &amp;&amp; nums[i+2] == 7)
+                return true;
+        }
+    }
+    return false;
+}
+##Solution 5 is:
+public boolean has77(int[] nums)
+{
+    for(int i = 0; i&lt;nums.length-1; i++)
+    {
+        if(nums[i]==7)
+        {
+        	if(nums[i+1] == 7)
+                return true;
+            else if(i &lt; nums.length-2 &amp;&amp; nums[i+2] == 7)
+                return true;
+        }
+    }
+    return false;
 }
 </t>
         </is>
@@ -1703,24 +3866,99 @@
       <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">Write a function in Java that implements the following logic: Return a version of the given array where each zero value in the array is replaced by the largest odd value to the right of the zero in the array. If there is no odd value to the right of the zero, leave the zero as a zero. Hint: in solving this: you may use a second helper function if you want, say to find the largest odd value to the right of a specified position.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] zeroMax(int[] nums)
 {
-    int max = 0;
-	for (int i = 0; i &lt; nums.length -1; i++)
+    int max;
+	for(int i = 0; i &lt; nums.length - 1; i++)
 	{
-		if (nums[i] == 0)
+		if(nums[i] == 0)
 		{
-			for (int x = i + 1; x &lt;= nums.length -1; x++)
+			max = 0;
+			for(int k = i + 1; k &lt; nums.length; k++)
 			{
-				if ( nums[x] &gt; max &amp;&amp; nums[x] % 2 == 1 )
-				max = nums[x];
+				if(nums[k] &gt; max &amp;&amp; nums[k] % 2 == 1)
+					max = nums[k];
 			}
-			nums[i] = max;
-			max = 0;
+			if(max != 0)
+				nums[i] = max;
 		}
 	}
-return nums;
+	return nums;
+}
+##Solution 2 is:
+public int[] zeroMax(int[] nums)
+{
+    int max = 0;
+    for (int j = 0; j &lt; nums.length - 1; j++)
+    {
+        if (nums[j] == 0)
+        {
+            for (int i = j + 1; i &lt;= nums.length - 1; i++)
+            {
+                if (nums[i] &gt; max &amp;&amp; nums[i] %2 == 1)
+                    max = nums[i];
+            }
+            nums[j] = max;
+            max = 0;
+        }
+    }
+    return nums;
+}
+##Solution 3 is:
+public int[] zeroMax(int[] nums)
+{
+    int max;
+	for(int i = 0; i &lt; nums.length - 1; i++)
+	{
+		if(nums[i] == 0)
+		{
+			max = 0;
+			for(int k = i + 1; k &lt; nums.length; k++)
+			{
+				if(nums[k] &gt; max &amp;&amp; nums[k] % 2 == 1)
+					max = nums[k];
+			}
+			if(max != 0)
+				nums[i] = max;
+		}
+	}
+	return nums;
+}
+##Solution 4 is:
+public int[] zeroMax(int[] nums)
+{
+    int max = 0;
+	for ( int i = nums.length - 1; i &gt;= 0; i--) {
+    	if (nums[i] !=0 &amp;&amp; nums[i] % 2==1 &amp;&amp; max&lt;nums[i]) {
+      		max=nums[i];
+    	}
+    	if(nums[i]==0){
+    		nums[i]=max;
+    	}
+  	}
+  	return nums;
+}
+##Solution 5 is:
+public int[] zeroMax(int[] nums)
+{
+    int max;
+	for(int i = 0; i &lt; nums.length - 1; i++)
+	{
+		if(nums[i] == 0)
+		{
+			max = 0;
+			for(int k = i + 1; k &lt; nums.length; k++)
+			{
+				if(nums[k] &gt; max &amp;&amp; nums[k] % 2 == 1)
+					max = nums[k];
+			}
+			if(max != 0)
+				nums[i] = max;
+		}
+	}
+	return nums;
 }
 </t>
         </is>
@@ -1733,83 +3971,98 @@
       <c r="A39" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an array of int values, return true if the group of n numbers at the start of the array is the same as the group of n numbers at the end of the array. For example, with {5, 6, 45, 99, 13, 5, 6}, the ends are the same for n == 0 and n == 2, and false for n == 1 and n == 3. You may assume that n is in the range 0..nums.length, inclusive.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean sameEnds(int[] nums, int n)
 {
-    if (n == 0)
-    {
-        if (nums.length == 0)
+    int[] a = new int[n];
+    int[] b = new int[n];
+    if (n == 0 | n == nums.length)
+    {
+        return true;
+    }
+    else
+    {
+        for (int i = 0; i &lt; n; i++)
+        {
+            a[i] = nums[i];
+            b[i] = nums[nums.length - n +i];
+            if (a[i] != b[i])
+            {
+                return false;
+            }
+        }
+    	return true;
+    }
+}
+##Solution 2 is:
+public boolean sameEnds(int[] nums, int n)
+{
+    int size = nums.length ;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+    	if ( i &lt; n)
+        {
+        	if (nums[i] != nums[size - (n-i)])
+                return false;
+        }
+    }
+                return true;
+}
+##Solution 3 is:
+public boolean sameEnds(int[] nums, int n)
+{
+        if (n == 0)
         {
             return true;
         }
-        else if (nums[0] == nums[nums.length - 1])
+        if (n == 1)
+        {
+            if (nums[0] == nums[nums.length - 1])
+                return true;
+        }
+        if (n == 2)
+        {
+            if (nums[0] == nums[nums.length - 2] &amp;&amp; nums[1] == nums[nums.length - 1])
+            {
+                return true;
+            }
+        }
+        if (n == 3 &amp;&amp; nums[0] == 1)
         {
             return true;
         }
-        else
-        {
+    if (n == 5)
+        return true;
+    return false;
+}
+##Solution 4 is:
+public boolean sameEnds(int[] nums, int n)
+{
+    int beg = 0;
+    int stop = nums.length-n;
+    for (; n &gt; 0; n--)
+    {
+        	if (nums[beg] != nums[stop])
+        	{
+            	return false;
+        	}
+        	else
+            {
+                beg++;
+                stop++;
+            }
+    }
+    return true;
+}
+##Solution 5 is:
+public boolean sameEnds(int[] nums, int n)
+{
+   for(int i = 0; i &lt; n; i++) {
+        if(nums[i] != nums[nums.length - n + i])
             return false;
-        }
-    }
-    else if (n == 1)
-    {
-        if (nums[0] == nums[nums.length - n])
-        {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
-    }
-    else if (n == 2)
-    {
-        if (nums[0] == nums[nums.length - n] &amp;&amp; nums[n - 1] == nums[nums.length - 1])
-        {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
-    }
-    else if (n == 3)
-    {
-        if (nums[0] == nums[nums.length - n] &amp;&amp; nums[n - 1] == nums[nums.length - 1] &amp;&amp; nums[n-2] == nums[nums.length-2])
-        {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
-    }
-    else if (n == 4)
-    {
-        if (nums[0] == nums[nums.length - n] &amp;&amp; nums[n - 1] == nums[nums.length - 1] &amp;&amp; nums[n-2] == nums[nums.length-2] &amp;&amp; nums[n-3] == nums[nums.length-3])
-        {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
-    }
-    else if (n == 5)
-    {
-        if (nums[0] == nums[nums.length - n] &amp;&amp; nums[n - 1] == nums[nums.length - 1] &amp;&amp; nums[n-2] == nums[nums.length-2] &amp;&amp; nums[n-3] == nums[nums.length-3] &amp;&amp; nums[n-4] == nums[nums.length-4])
-        {
-            return true;
-        }
-        else
-        {
-            return false;
-        }
-    }
-    else
-    {
-        return false;
-    }
+    }
+    return true;
 }
 </t>
         </is>
@@ -1822,30 +4075,104 @@
       <c r="A40" t="inlineStr">
         <is>
           <t xml:space="preserve">Say that a "clump" in an array is a series of 2 or more adjacent elements of the same value. Return the number of clumps in the given array.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int countClumps(int[] nums)
 {
-    int a = 0;
-    for (int i = 0; i &lt; nums.length - 1; i++)
-    {
-        if (nums[i] == nums[i + 1])
-        {
-            a++;
-        }
-        if (i + 2 &lt; nums.length &amp;&amp; nums[i] == nums[i + 1] &amp;&amp; nums[i] == nums[i + 2])
-        {
-            i++;
-        }
-        if (i + 3 &lt; nums.length &amp;&amp; nums[i] == nums[i + 1] &amp;&amp; nums[i] == nums[i + 2] &amp;&amp; nums[i] == nums[i + 3])
-        {
-            i = i + 2;
-        }
-        if (i + 4 &lt; nums.length &amp;&amp; nums[i] == nums[i + 1] &amp;&amp; nums[i] == nums[i + 2] &amp;&amp; nums[i] == nums[i + 3] &amp;&amp; nums[i] == nums[i + 4])
-        {
-            i = i + 3;
-        }
-    }
-    return a;
+    int clumps = 0;
+	boolean isClump = false;
+  for(int i = 0; i &lt; nums.length - 1; i++)
+  {
+  	if(isClump)
+  	{
+	  	if(nums[i] != nums[i+1])
+	  		isClump = false;
+	  }
+  	else if(nums[i] == nums[i+1])
+  	{
+  		isClump = true;
+  		clumps++;
+  	}
+  }
+  return clumps;
+}
+##Solution 2 is:
+public int countClumps(int[] nums)
+{
+    int len = nums.length;
+    int clumps = 0;
+    for (int i = 0; i &lt; len-1; i++)
+    {
+        if (nums[i] == nums[i +1])
+        {
+        	int j = i;
+        	while (j &lt; len - 1)
+        	{
+            	if (nums[j] != nums[i])
+            	{
+            		break;
+            	}
+            	i = j;
+            	j++;  
+        	}
+            clumps++;
+        }
+    }
+    return clumps;
+}
+##Solution 3 is:
+public int countClumps(int[] nums)
+{
+    	int clump = 0;
+	boolean clumpOrNo = true;
+  for(int i = 0; i &lt; nums.length - 1; i++)
+  {
+  	if(!clumpOrNo)
+  	{
+	  	if(nums[i] != nums[i+1])
+	  		clumpOrNo = true;
+	  }
+  	else if(nums[i] == nums[i+1])
+  	{
+  		clumpOrNo = false;
+  		clump++;
+  	}
+  }
+  return clump;
+}
+##Solution 4 is:
+public int countClumps(int[] nums)
+{
+    int c = 0;
+    int a = 123;
+    for(int i = 0; i &lt; nums.length-1; i++)
+	{
+		if(nums[i] == nums[i+1] &amp;&amp; nums[i] != a)
+        {
+            	a = nums[i];
+                c++;
+        }
+        else if (nums[i] != nums[i+1])
+        {
+            a = 123;
+        }
+	}  
+    return c;
+}
+##Solution 5 is:
+public int countClumps(int[] nums) {
+  int current = -1, clump = 0;
+  for(int i = 0; i &lt; nums.length - 1; i++) {
+    if(nums[i] == nums[i + 1] &amp;&amp; nums[i] != current) {
+       current = nums[i];
+       clump++;
+    } else {
+       if(nums[i] != current) {
+          current = -1;
+       }
+    }
+  }
+  return clump;
 }
 </t>
         </is>
@@ -1858,20 +4185,91 @@
       <c r="A41" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an array, return an array that contains exactly the same numbers as the original array, but rearranged so that every 4 is immediately followed by a 5. Do not move the 4's, but every other number may move. The array contains the same number of 4's and 5's, and every 4 has a number after it that is not a 4. In this version, 5's may appear anywhere in the original array. (This is a slightly harder version of the fix34 problem.)
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
+public int[] fix45(int[] nums)
+{
+    int x = 0;
+    for(int i = 0; i&lt; nums.length - 1; i++)
+    {
+     if (nums[i] == 4 &amp;&amp; nums[i+1] != 5)
+     {
+      for(; !(nums[x] == 5 &amp;&amp; (x == 0 || x&gt; 0 &amp;&amp; nums[x-1] !=4)); x++);
+          nums[x] = nums[i+1];
+         nums[i+1] = 5;
+     }
+    }
+    return nums;
+}
+##Solution 2 is:
 public int[] fix45(int[] nums)
 {
     int j = 0;
 	for(int i = 0; i &lt; nums.length - 1; i++)
 	{
-		if(nums[i] == 4 &amp;&amp; nums[i+1] != 5)
+		if(nums[i] == 4 &amp;&amp; nums[i + 1] != 5)
 		{
-			for(; !(nums[j] == 5 &amp;&amp; (j == 0 || j &gt; 0 &amp;&amp; nums[j-1] != 4)); j++);
-			nums[j] = nums[i+1];
-			nums[i+1] = 5;
+			for(; !(nums[j] == 5 &amp;&amp; (j == 0 || j &gt; 0 &amp;&amp; nums[j                   - 1] != 4)); j++);
+			nums[j] = nums[i + 1];
+			nums[i + 1] = 5;
 		}
 	}
 	return nums;
+}
+##Solution 3 is:
+public int[] fix45(int[] nums)
+{ 
+    int j = 0;
+    for (int i = 0; i &lt; nums.length -1; i++)
+    {
+     	if (nums[i] == 4 &amp;&amp; nums[i + 1] != 5)
+        {
+			for (; !(nums[j] == 5 &amp;&amp; (j == 0 || j &gt; 0 &amp;&amp; nums[j-1] != 4)); j++);
+                              {
+                                  nums[j] = nums[i + 1];
+                                  nums[i + 1] = 5;
+                              }
+        }
+    }
+    return nums;
+}
+##Solution 4 is:
+public int[] fix45(int[] nums)
+{
+    int i = 0;
+    int j = 0;
+    while(j &lt; nums.length &amp;&amp; nums[j] != 5)
+        j++;
+    while(i &lt; nums.length)
+    {
+    	if(nums[i] == 4)
+        {
+        	int temp = nums[i+1];
+            nums[i+1] = nums[j];
+            nums[j] = temp;
+            while((j &lt; nums.length &amp;&amp; nums[j] != 5) || j ==i+1)
+                j++;
+        }
+        i++;
+    }
+    return nums;
+}
+##Solution 5 is:
+public int[] fix45(int[] nums)
+{
+    int j = 0;
+      for (int i = 0; i &lt; nums.length - 1; ++i) {
+        if (nums[i] == 4 &amp;&amp; nums[i + 1] != 5) 
+        {
+          while (nums[j] != 5 || (j != 0 &amp;&amp; nums[j - 1] == 4)) 
+          {
+            j++;
+          }
+          nums[j] = nums[i + 1];
+          nums[i + 1] = 5;
+        }
+      }
+      return nums;
 }
 </t>
         </is>
@@ -1884,44 +4282,121 @@
       <c r="A42" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an int array, return the sum of the numbers in the array, except ignore sections of numbers starting with a 6 and extending to the next 7 (every 6 will be followed by at least one 7). Return 0 for no numbers.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int sum67(int[] nums)
 {
     int sum = 0;
-    if (nums.length == 0)
-    {
-        return 0;
-    }
-    else
-    {
-        for (int i = 0; i &lt; nums.length; i++)
-        {
-            if (nums[i] == 6)
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        sum += nums[i];
+        if (nums[i] == 6)
+        {
+            sum -= 6;
+            for (int j = i; nums[j] != 7; j++)
             {
-                if (nums[i + 1] == 7)
+                if (j == nums.length - 1)
                 {
-                    i = i + 1;
+                    return sum;
                 }
-                else if (nums[i + 2] == 7)
+                else
                 {
-                    i = i + 2;
-                }
-                else if (nums[i + 3] == 7)
-                {
-                    i = i + 3;
-                }
-                else if (nums[i + 4] == 7)
-                {
-                    i = i + 4;
+                    i = j + 1;
                 }
             }
-            else
+        }
+    }
+    return sum;
+}
+##Solution 2 is:
+public int sum67(int[] nums)
+{
+    int count = 0;
+    int sum = 0;
+    for(int i = 0; i &lt; nums.length; i++)
+    {
+        if(nums[i] == 6)
+        {
+            for(int x = 1; x &lt; nums.length - i; i++)
             {
-                sum = sum + nums[i];
+                if(nums[i+x] == 7)
+                {
+                    count = i + x;
+                    break;
+                }
             }
+            i = count;
+        }
+        else
+        {
+            sum = sum + nums[i];
+        }
+    }
+   return sum;
+}
+##Solution 3 is:
+public int sum67(int[] nums)
+{
+    int sum = 0;
+int annul7=0;
+  for (int i =0 ; i &lt;nums.length;i++)
+  {
+  if(nums[i] == 6)
+  {
+  for( int j = i; nums[j] != 7;j++)
+  {
+  nums[j] = 0;
+  annul7 = j;
+  }
+   nums[annul7+1] =0;
+  }
+  else
+    sum += nums[i];
+    }
+    return sum;
+}
+##Solution 4 is:
+public int sum67(int[] nums)
+{
+    int sum = 0;
+        if (nums.length &lt; 1) {
+            return 0;
+        }
+        for (int i = 0; i &lt; nums.length; i++) {
+            if (nums[i] == 6) {
+                while (nums[i] != 7) {
+                    i++;
+                }
+            } else {
+                sum += nums[i];
+            }
         }
         return sum;
-    }
+}
+##Solution 5 is:
+public int sum67(int[] nums)
+{
+    int sum = 0;
+    boolean sixMode = false;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        if (sixMode)
+        {
+            if (nums[i] == 7)
+            {
+                sixMode = false;
+            }
+        }
+        else if (nums[i] == 6)
+        {
+            sixMode = true;
+        }
+        else
+        {
+            sum += nums[i];
+        }
+    }
+    return sum;
 }
 </t>
         </is>
@@ -1934,20 +4409,88 @@
       <c r="A43" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an int[] array, write a function that returns an array where all the 10's have been removed. The remaining elements should shift left towards the start of the array as needed, and the empty spaces at the end of the array should be set to 0. So {1, 10, 10, 2} yields {1, 2, 0, 0}. You may modify and return the given array or make a new array.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] withoutTen(int[] nums)
 {
-    int[] arr = new int[nums.length];
+    int[] newArray = new int[nums.length];
+    int numZero = 0;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        if (nums[i] != 10)
+        {
+            newArray[numZero] = nums[i];
+            numZero++;
+        }
+    }
+    for (int i = numZero; i &lt; nums.length; i++)
+    {
+        newArray[i] = 0;
+    }
+    return newArray;
+}
+##Solution 2 is:
+public int[] withoutTen(int[] nums)
+{
+    	int[] array = new int[nums.length];
+	int pee = 0;
+	for(int i = 0; i &lt; nums.length; i++)
+	{
+		if(nums[i] != 10)
+		{
+			array[pee] = nums[i];
+			pee++;
+		}
+	}
+	return array;
+}
+##Solution 3 is:
+public int[] withoutTen(int[] nums)
+{
+        int[] copy = new int[nums.length];
+    int index = 0;
+    for (int i = 0; i &lt; nums.length; i++)
+        if (nums[i] != 10) {
+            copy[index] = nums[i];
+            index++;
+        }
+    return copy;
+}
+##Solution 4 is:
+public int[] withoutTen(int[] nums)
+{
+    int[] news = new int[nums.length];
     int j = 0;
-    for (int i = 0; i &lt; nums.length; i++)
-    {
-        if (nums[i] != 10)
-        {
-            arr[j] = nums[i];
-            j++;
-        }
-    }
-    return arr;
+    for (int i =0; i&lt;nums.length;i++)
+         {
+             if(nums[i]!=10)
+             {
+                 news[j]=nums[i];
+                 j++;
+             }
+         }
+    for (int i =j; i&lt;nums.length;i++)
+         {
+             news[i]=0;
+         }
+         return news;
+}
+##Solution 5 is:
+public int[] withoutTen(int[] nums)
+{
+    int[] neww = new int[nums.length];
+    int x = 0;
+    int y = 0;
+    for(int i = 0; i &lt; nums.length; i++)
+	{
+		if(nums[i] != 10)
+        {
+            neww[x] = nums[i];
+            x++;
+            y++;
+        }
+    }
+    return neww;
 }
 </t>
         </is>
@@ -1960,18 +4503,110 @@
       <c r="A44" t="inlineStr">
         <is>
           <t xml:space="preserve">For each multiple of 10 in the given array, change all the values following it to be that multiple of 10, until encountering another multiple of 10. So {2, 10, 3, 4, 20, 5} yields {2, 10, 10, 10, 20, 20}.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] tenRun(int[] nums)
 {
-    int x = -1;
-	for(int i = 0; i &lt; nums.length; i++)
-	{
-		if(nums[i] % 10 == 0)
-			x = nums[i];
-		else if(x != -1)
-			nums[i] = x;
-	}
-	return nums;
+        boolean replace = false;
+    int multiple = 0;
+    for (int i = 0; i &lt; nums.length; i++) {
+        if (nums[i] % 10 == 0) {
+            if (!replace) {
+                replace = true;
+                multiple = nums[i];
+            } else
+                multiple = nums[i];
+        }
+        if (nums[i] % 10 != 0 &amp;&amp; replace) nums[i] = multiple;
+    }
+    return nums;
+}
+##Solution 2 is:
+public int[] tenRun(int[] nums)
+{
+    int length = nums.length;
+    if (length &lt; 1) 
+    {
+            return nums;
+        }
+        int bhag = nums[0];
+        for (int counter = 0; counter &lt; length; counter++)
+        {
+            if (nums[counter] % 10 == 0) 
+            {
+                bhag = nums[counter];
+            }
+            if (bhag % 10 != 0)
+            {
+                bhag = nums[counter];
+            }
+            else
+            {
+             nums[counter] = bhag;
+            }
+        }
+        return nums;
+}
+##Solution 3 is:
+public int[] tenRun(int[] nums)
+{
+    int current = -1;
+    for (int i = 0; i &lt; nums.length; i++)
+    {
+        if (nums[i]%10 == 0)
+        {
+            current = nums[i];
+        }
+        else if (current != -1)
+        {
+            nums[i] = current;
+        }
+    }
+    return nums;
+}
+##Solution 4 is:
+public int[] tenRun(int[] nums)
+{
+   int[] newarray = new int[nums.length];
+    int b = 0;
+    for(int a = 0; a &lt; nums.length; a++)
+    {
+    	if(nums[a] %10 != 0)
+    	{
+    	newarray[a] = nums[a];
+            b = b + 1; 
+    	}
+        else 
+        {
+        break;
+        }
+    }
+    int c = 0;
+    for(int i = b; i &lt; nums.length; i++)
+    {
+    	if(nums[i] %10 == 0)
+    	{
+            c = i;
+    	}
+        newarray[i] = nums[c];
+    }
+    return newarray;
+}
+##Solution 5 is:
+public int[] tenRun(int[] nums) {
+    boolean replace = false;
+    int multiple = 0;
+    for (int i = 0; i &lt; nums.length; i++) {
+        if (nums[i] % 10 == 0) {
+            if (!replace) {
+                replace = true;
+                multiple = nums[i];
+            } else
+                multiple = nums[i];
+        }
+        if (nums[i] % 10 != 0 &amp;&amp; replace) nums[i] = multiple;
+    }
+    return nums;
 }
 </t>
         </is>
@@ -1984,25 +4619,110 @@
       <c r="A45" t="inlineStr">
         <is>
           <t xml:space="preserve">Return the centered average of an array of ints, which we'll say is the mean average of the values, except ignoring the largest and smallest values in the array. If there are multiple copies of the smallest value, ignore just one copy, and likewise for the largest value. Use int division to produce the final average. You may assume that the array has a length of 3 or more.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int centeredAverage(int[] nums)
 {
+    int max = -100000;
+    int min = 100000;
+    int sum = 0;
+    for (int n : nums)
+    {
+    	if (n &gt; max)
+            max = n;
+        if (n &lt; min)
+            min = n;
+        sum += n;
+    }
+    return (sum - max - min)/(nums.length - 2);
+}
+##Solution 2 is:
+public int centeredAverage(int[] nums)
+{
     int max = nums[0];
+	int min = nums[0];
+	int sum = nums[0];
+	for(int i = 1; i &lt; nums.length; i++)
+	{
+		sum  += nums[i];
+		if(nums[i] &gt; max)
+			max = nums[i];
+		else if(nums[i] &lt; min)
+			min = nums[i];
+	}
+	return (sum-max-min) / (nums.length - 2);
+}
+##Solution 3 is:
+public int centeredAverage(int[] nums)
+{
+    int small = 999999;
+    int large =-999999;
+    int sum = 0;
+    for(int i =0; i&lt;nums.length;i++)
+    {
+        sum = sum + nums[i];
+        if (nums[i]&lt;small)
+        {
+            small = nums[i];
+        }
+        if (nums[i]&gt;large)
+        {
+            large = nums[i];
+        }
+    }
+    sum = sum - small - large;
+    return sum/(nums.length-2);
+}
+##Solution 4 is:
+public int centeredAverage(int[] nums)
+{
+     int sum = 0;
     int min = nums[0];
+    int max = nums[1];
+    for(int i = 0; i &lt; nums.length; i++) {
+         max = Math.max(max, nums[i]);
+        sum += nums[i];
+        min = Math.min(min, nums[i]);
+    }
+    int result = (sum - min - max) / (nums.length - 2);                      
+    return result ;
+}
+##Solution 5 is:
+public int centeredAverage(int[] nums)
+{
+    int min = 1000;
+    int max = -1000;
     int sum = 0;
-    for (int i = 0; i &lt; nums.length; i++)
-    {
-        if (nums[i] &gt; max)
-        {
-            max = nums[i];
-        }
-        else if (nums[i] &lt; min)
-        {
-            min = nums[i];
-        }
-        sum = sum + nums[i];
-    }
-    return (sum - min - max)/(nums.length - 2);
+    int posMin = 0;
+    int posMax =0;
+    int count = 0;
+    for (int i = 0; i&lt;nums.length;i++)
+    {
+        if(nums[i]&lt;min)
+        {
+            min=nums[i];
+            posMin = i;
+        }
+        if(nums[i]&gt;max)
+        {
+            max=nums[i];
+            posMax = i;
+        }
+    }
+    if(posMin==posMax)
+    {
+        posMin++;
+    }
+    for (int j = 0; j&lt;nums.length; j++)
+    {
+        if(j!=posMin &amp;&amp; j!=posMax)
+        {
+            sum+=nums[j];
+            count++;
+        }
+    }
+    int avg = sum/count;
+    return avg;
 }
 </t>
         </is>
@@ -2015,14 +4735,53 @@
       <c r="A46" t="inlineStr">
         <is>
           <t xml:space="preserve">Given a number n, create and return a new int array of length n, containing the numbers 0, 1, 2, ... n-1. The given n may be 0, in which case just return a length 0 array. You do not need a separate if statement for the length-0 case; the for loop should naturally execute 0 times in that case, so it just works. The syntax to make a new int array is new int[desired_length].
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] fizzArray(int n)
 {
+    int count = 0;
+    int[] newArray = new int[n];
+    for (int i = 0; i &lt; n; i++)
+    {
+        newArray[i] = count;
+        count ++;
+    }
+    return newArray;
+}
+##Solution 2 is:
+public int[] fizzArray(int n)
+{
+    int[] q = new int[n];
+    for(int i=0;i&lt;q.length;i++)
+    {
+        q[i]=i;
+    }
+    return q;
+}
+##Solution 3 is:
+public int[] fizzArray(int n)
+{
     int[] arr = new int[n];
+    for(int i = 0; i &lt; n; i++)
+        arr[i] = i;
+    return arr;
+}
+##Solution 4 is:
+public int[] fizzArray(int n)
+{
+    int[] array = new int[n];
     for (int i = 0; i &lt; n; i++)
     {
+        array[i] = i;
+    }
+    return array;
+}
+##Solution 5 is:
+public int[] fizzArray(int n)
+{
+     int[] arr = new int[n];
+    for(int i = 0; i &lt; n; i++)
         arr[i] = i;
-    }
     return arr;
 }
 </t>
@@ -2036,30 +4795,109 @@
       <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">Consider the series of numbers beginning at start and running up to but not including end, so for example start=1 and end=5 gives the series 1, 2, 3, 4. Return a new String[] array containing the string form of these numbers, except in the case of multiples of 3, use "Fizz" instead of the number, and for multiples of 5 use "Buzz", and for multiples of both 3 and 5 use "FizzBuzz". In Java, String.valueOf(xxx) will make the String form of an int or other type.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public String[] fizzBuzz(int start, int end)
 {
     String[] arr = new String[end - start];
-    for (int i = 0; i &lt; arr.length; i++)
-    {
-        if ((i + start) % 3 == 0 &amp;&amp; (i + start) % 5 == 0)
-        {
-            arr[i] = "FizzBuzz";
-        }
-        else if ((i + start) % 3 == 0)
-        {
-            arr[i] = "Fizz";
-        }
-        else if ((i + start) % 5 == 0)
-        {
-            arr[i] = "Buzz";
-        }
+    for(int i = start; i &lt; end; i++) {
+        if(i % 15 == 0) {
+            arr[i - start] = "FizzBuzz";
+        } else if(i % 3 == 0) {
+            arr[i - start] = "Fizz";
+        } else if(i % 5 == 0) {
+            arr[i - start] = "Buzz";
+        } else {
+            arr[i - start] = String.valueOf(i);
+        }
+    }
+    return arr;
+}
+##Solution 2 is:
+public String[] fizzBuzz(int start, int end)
+{
+    String[] newa = new String [end - start];
+    for (int i = 0; start &lt; end; i++)
+    {
+        if (start % (15) == 0)
+            newa[i] = "FizzBuzz";
+        else if (start % 3 == 0)
+            newa[i] = "Fizz";
+        else if (start % 5 == 0)
+            newa[i] = "Buzz";
         else
-        {
-            arr[i] = String.valueOf(start + i);
-        }
-    }
-    return arr;
+            newa[i] = String.valueOf(start);
+        start++;
+    }
+    return newa;
+}
+##Solution 3 is:
+public String[] fizzBuzz(int start, int end)
+{
+    String[] newArr = new String[end - start];
+        for (int i = 0; start &lt; end; i++) {
+        	if((start % (3*5)) == 0){
+                 newArr[i] = "FizzBuzz";
+            } else if((start % 3) == 0){
+                newArr[i] = "Fizz";
+            } else if((start % 5) == 0){
+                newArr[i] = "Buzz";
+            } else{
+                newArr[i] = String.valueOf(start);
+            }
+           start++;
+        }
+        return newArr;
+}
+##Solution 4 is:
+public String[] fizzBuzz(int start, int end)
+{
+    String[] fizz = new String[end - start];
+    for(int i = start; i &lt; end; i++) 
+    {
+        if(i % 15 == 0) 
+        {
+            fizz[i - start] = "FizzBuzz";
+        } 
+        else if(i % 3 == 0) 
+        {
+            fizz[i - start] = "Fizz";
+        } 
+        else if(i % 5 == 0) 
+        {
+            fizz[i - start] = "Buzz";
+        } 
+        else 
+        {
+            fizz[i - start] = String.valueOf(i);
+        }
+    }                                                   
+    return fizz;
+}
+##Solution 5 is:
+public String[] fizzBuzz(int start, int end)
+{
+    String[] a = new String[end - start];
+    for (int i = start; i &lt; end; i++)
+    {
+     	if (i % 15 == 0)
+        {
+         	a[i - start] = "FizzBuzz";
+        }
+        else if (i % 3 == 0)
+        {
+         	a[i - start] = "Fizz";   
+        }
+        else if (i % 5 == 0)
+        {
+         	a[i - start] = "Buzz";   
+        }
+        else
+        {
+         	a[i - start] = String.valueOf(i);   
+        }
+    }
+    return a;
 }
 </t>
         </is>
@@ -2072,65 +4910,82 @@
       <c r="A48" t="inlineStr">
         <is>
           <t xml:space="preserve">Given an array of ints, return true if every 2 that appears in the array is next to another 2. Otherwise, return false.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean twoTwo(int[] nums)
 {
-    int q = 0;
-    for (int i = 0; i &lt; nums.length; i++)
-    {
-        if (nums.length == 1 &amp;&amp; nums[i] != 2)
-        {
-            return true;
-        }
-        if (nums[i] == 2)
-        {
-            if (nums.length == 1)
-            {
-                return false;
-            }
-        else if (i == 0)
-        {
-            if (nums[i + 1] == 2)
-            {
-                q = q + 0;
-            }
-            else
-            {
-                q = q + 100;
-            }
-        }
-        else if (i == nums.length - 1)
-        {
-            if (nums[i - 1] == 2)
-            {
-                q += 0;
-            }
-            else
-            {
-                q += 100;
-            }
-        }
-        else
-        {
-            if (nums[i - 1] == 2 || nums[i + 1] == 2)
-            {
-                q += 0;
-            }
-            else
-            {
-                q += 100;
-            }
-        }
-        }
-    }
-    if ( q &gt;= 100)
-    {
+    if(nums.length == 1 &amp;&amp; nums[0] == 2)
         return false;
-    }
-    else
-    {
+    if(nums.length &gt;= 2 &amp;&amp; ((nums[0] == 2 &amp;&amp; nums[1] != 2) ||
+        (nums[nums.length-1] == 2 &amp;&amp; nums[nums.length-2] != 2)))
+        return false;
+    for(int i = 1; i &lt;= nums.length - 2; i++) {
+        if(nums[i] == 2 &amp;&amp; nums[i-1] != 2 &amp;&amp; nums[i+1] != 2)
+            return false;
+    }
+    return true;
+}
+##Solution 2 is:
+public boolean twoTwo(int[] nums)
+{
+    if (nums.length == 0)
         return true;
-    }
+    if (nums.length == 1 &amp;&amp; nums[0] == 2)
+        return false;
+    if (nums[0] == 2 &amp;&amp; nums[1] != 2)
+        return false;
+    if (nums[nums.length - 1] == 2 &amp;&amp; nums[nums.length - 2] != 2)
+        return false;
+    for (int i = 1; i &lt; nums.length - 1; i++)
+        if (nums[i - 1] != 2 &amp;&amp; nums[i] == 2 &amp;&amp; nums[i + 1] != 2)
+            return false;
+    return true;
+}
+##Solution 3 is:
+public boolean twoTwo(int[] nums)
+{
+    int count = 0;
+	for(int i = 0; i &lt; nums.length; i++)
+	{
+		if(nums[i] == 2)
+			count++;
+		else
+		{
+			if(count == 1)
+				return false;
+			else
+				count = 0;
+		}
+	}
+	return (count != 1);
+}
+##Solution 4 is:
+public boolean twoTwo(int[] nums)
+{
+    if(nums.length == 1 &amp;&amp; nums[0] == 2)
+        return false;
+    if(nums.length &gt;= 2 &amp;&amp; ((nums[0] == 2 &amp;&amp; nums[1] != 2) ||
+        (nums[nums.length-1] == 2 &amp;&amp; nums[nums.length-2] != 2)))
+        return false;
+    for(int i = 1; i &lt;= nums.length - 2; i++) {
+        if(nums[i] == 2 &amp;&amp; nums[i-1] != 2 &amp;&amp; nums[i+1] != 2)
+            return false;
+    }
+    return true;
+}
+##Solution 5 is:
+public boolean twoTwo(int[] nums)
+{
+    if(nums.length == 1 &amp;&amp; nums[0] == 2)
+        return false;
+    if(nums.length &gt;= 2 &amp;&amp; ((nums[0] == 2 &amp;&amp; nums[1] != 2) ||
+        (nums[nums.length-1] == 2 &amp;&amp; nums[nums.length-2] != 2)))
+        return false;
+    for(int i = 1; i &lt;= nums.length - 2; i++) {
+        if(nums[i] == 2 &amp;&amp; nums[i-1] != 2 &amp;&amp; nums[i+1] != 2)
+            return false;
+    }
+    return true;
 }
 </t>
         </is>
@@ -2143,22 +4998,92 @@
       <c r="A49" t="inlineStr">
         <is>
           <t xml:space="preserve">Given a non-empty array, return true if there is a place to split the array so that the sum of the numbers on one side is equal to the sum of the numbers on the other side.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public boolean canBalance(int[] nums)
 {
-    int x = 0;
-	int y;
+    int t = nums.length;
+    int leftSum = 0;
+  	for (int i = 0; i &lt; nums.length; i++) 
+    {
+    	leftSum += nums[i];
+    	int rightSum = 0;
+    	for (int j = t - 1; j &gt; i; j--) 
+    	{
+      		rightSum += nums[j];
+    	}
+    	if (rightSum == leftSum)
+        {
+      		return true;
+        }
+  	}
+  	return false;
+}
+##Solution 2 is:
+public boolean canBalance(int[] nums)
+{
+    int first = 0;
+    int second = 0;
+    for(int i = 0; i &lt; nums.length; i++)
+        second += nums[i];
+    for(int i = 0; i &lt;= nums.length - 2; i++) {
+        first += nums[i];
+        second -= nums[i];
+        if(first == second)
+            return true;
+    }
+    return false;
+}
+##Solution 3 is:
+public boolean canBalance(int[] nums)
+{
+    int lSum = 0;
+    for (int i = 0; i &lt; nums.length; i++) 
+    {
+        lSum += nums[i];
+        int rSum = 0;
+        for (int j = nums.length-1; j &gt; i; j--) 
+        {
+            rSum += nums[j];
+        }
+        if (rSum == lSum)
+        {
+            return true;
+        }
+    }
+    return false;
+}
+##Solution 4 is:
+public boolean canBalance(int[] nums)
+{
+      int first = 0;
+    int second = 0;
+    for(int i = 0; i &lt; nums.length; i++)
+        second += nums[i];
+    for(int i = 0; i &lt;= nums.length - 2; i++) {
+        first += nums[i];
+        second -= nums[i];
+        if(first == second)
+            return true;
+    }
+return false;
+}
+##Solution 5 is:
+public boolean canBalance(int[] nums)
+{
+    int left = 0;
+	int right;
 	for(int i = 0; i &lt; nums.length - 1; i++)
-		x += nums[i];
-	y = nums[nums.length-1];
+		left += nums[i];
+	right = nums[nums.length-1];
 	for(int i = nums.length - 2; i &gt; 0; i--)
 	{
-		if(x == y)
+		if(left == right)
 			return true;
-		x -= nums[i];
-		y += nums[i];
+		left -= nums[i];
+		right += nums[i];
 	}
-	return (x == y);
+	return (left == right);
 }
 </t>
         </is>
@@ -2171,50 +5096,71 @@
       <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">Given n &gt;= 0, create an array with the pattern {1, 1, 2, 1, 2, 3, ... 1, 2, 3 .. n} (spaces added to show the grouping). Note that the length of the array will be 1 + 2 + 3 ... + n, which is known to sum to exactly n * (n + 1)/2.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] seriesUp(int n)
 {
+    int[] result = new int[n*(n+1)/2];
+    int m = 0;
+    for (int i = 0;i&lt;=n;i++)
+    {
+        for (int j = 1;j&lt;=i;j++, m++)
+        {
+            result[m] = j;
+        }
+    }
+        return result;
+}
+##Solution 2 is:
+public int[] seriesUp(int n)
+{
     int[] arr = new int[n*(n+1)/2];
-    for (int i = 0; i &lt; arr.length; i++)
-    {
-        arr[0] = 1;
-        if (n &gt; 1)
-        {
-            arr[1] = 1;
-            arr[2] = 2;
-        }
-        if (n &gt; 2)
-        {
-            arr[3] = 1;
-            arr[4] = 2;
-            arr[5] = 3;
-        }
-        if (n &gt; 3)
-        {
-            arr[6] = 1;
-            arr[7] = 2;
-            arr[8] = 3;
-            arr[9] = 4;
-        }
-        if (n &gt; 4)
-        {
-            arr[10] = 1;
-            arr[11] = 2;
-            arr[12] = 3;
-            arr[13] = 4;
-            arr[14] = 5;
-        }
-        if (n &gt; 5)
-        {
-            arr[15] = 1;
-            arr[16] = 2;
-            arr[17] = 3;
-            arr[18] = 4;
-            arr[19] = 5;
-            arr[20] = 6;
-        }
-    }
-            return arr;
+	int p = 0;
+	for(int i = 1; i &lt;= n; i++)
+	{
+		for(int j = 1; j &lt;= i; j++, p++)
+			arr[p] = j;
+	}
+	return arr;
+}
+##Solution 3 is:
+public int[] seriesUp(int n)
+{
+    int[] array = new int[n*(n+1)/2];
+    int s = 0;
+    for(int i = 1; i &lt;= n; i++)
+    {
+        for(int j = 1; j &lt;= i; j++)
+        {
+            array[s] = j;
+            s++;
+        }
+    }
+    return array;
+}
+##Solution 4 is:
+public int[] seriesUp(int n)
+{
+    int[] array = new int[n*(n+1)/2];
+	int element = 0;
+	for(int i = 1; i &lt;= n; i++)
+	{
+		for(int j = 1; j &lt;= i; j++, element++)
+			array[element] = j;
+	}
+	return array;
+}
+##Solution 5 is:
+public int[] seriesUp(int num)
+{
+    	int[] array = new int[num*(num+1)/2];
+	int pee = 0;
+	for(int i = 1; i &lt;= num; i++)
+	{
+		for(int j = 1; j &lt;= i; j++, pee++)
+			array[pee] = j;
+	}
+	return array;
 }
 </t>
         </is>
@@ -2227,29 +5173,82 @@
       <c r="A51" t="inlineStr">
         <is>
           <t xml:space="preserve">Return an array that is "left shifted" by one--so for an input of {6, 2, 5, 3}, the method returns {2, 5, 3, 6}. You may modify and return the given array, or return a new array.
-##The solution of the given exercise is:
+##Here are 5 correct solutions to the provided exercise:
+##Solution 1 is:
 public int[] shiftLeft(int[] nums)
 {
-    if (nums.length &gt; 0)
-    {
-        int x = nums[0];
-    for (int i = 0; i &lt; nums.length; i++)
-    {
-        if (i &lt; nums.length - 1)
-        {
-            nums[i] = nums [i + 1];
-        }
-        else
-        {
-            nums[i] = x;
-        }
-    }
+    if (nums.length == 0)
+    {
+     	return nums;   
+    }
+    int [] shifted = new int[nums.length];
+    shifted[nums.length-1] = nums[0];
+    for (int i = 0; i &lt; nums.length-1; i++)
+    {
+        shifted[i] = nums[i+1];
+    }
+    return shifted;
+}
+##Solution 2 is:
+public int[] shiftLeft(int[] nums)
+{
+    if (nums.length == 0)
+    {
+        return nums;
+    }
+    int first = nums[0];
+    int last = nums[nums.length - 1];
+    for (int i = 0; i &lt; nums.length - 1; i++)
+    {
+        nums[i] = nums[i + 1];
+    }
+    nums[nums.length - 1] = first;
     return nums;
-    }
-    else
-    {
-        return nums;
-    }
+}
+##Solution 3 is:
+public int[] shiftLeft(int[] nums)
+{
+	if(nums.length &gt;= 2)
+	{
+		int temp = nums[0];
+		for(int i = 0; i &lt; nums.length - 1; i++)
+			nums[i] = nums[i+1];
+		nums[nums.length-1] = temp;
+	}
+	return nums;
+}
+##Solution 4 is:
+public int[] shiftLeft(int[] nums)
+{
+    if(nums.length &gt;= 2)
+	{
+		int temp = nums[0];
+		for(int i = 0; i &lt; nums.length - 1; i++)
+			nums[i] = nums[i+1];
+		nums[nums.length-1] = temp;
+	}
+	return nums;
+}
+##Solution 5 is:
+public int[] shiftLeft(int[] nums)
+{
+    int t = nums.length;
+    int[] answer = new int[t];
+  	if (t == 0)
+    {
+    	return answer;
+    }
+  	for (int i = 0; i &lt; t - 1; i++) 
+    {
+    	if (i &gt; 0)
+      	answer[i] = nums[i + 1];
+  	}
+  	if (t &gt; 1)
+    {
+    answer[0] = nums[1];
+    }
+  	answer[t - 1] = nums[0];
+  	return answer;
 }
 </t>
         </is>
